--- a/result.xlsx
+++ b/result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ataraxia\Documents\VscodeDOC\FSSP\FSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F875B3C3-BD99-41C8-A287-AA1D344CB978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E252161-5F87-4B43-9B16-5D06E4C86DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4440" windowWidth="23016" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="925">
   <si>
     <t>Episode 4, Reward: -75036</t>
   </si>
@@ -2329,6 +2329,480 @@
   <si>
     <t>Episode 3, Reward: -48999</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Episode 1, Reward: -217510, Makespan: 888.37h</t>
+  </si>
+  <si>
+    <t>Episode 2, Reward: -260316, Makespan: 665.83h</t>
+  </si>
+  <si>
+    <t>Episode 3, Reward: -51443, Makespan: 528.83h</t>
+  </si>
+  <si>
+    <t>Episode 4, Reward: -51443, Makespan: 528.83h</t>
+  </si>
+  <si>
+    <t>Episode 5, Reward: -51443, Makespan: 528.83h</t>
+  </si>
+  <si>
+    <t>Episode 6, Reward: -51443, Makespan: 528.83h</t>
+  </si>
+  <si>
+    <t>Episode 7, Reward: -51443, Makespan: 528.83h</t>
+  </si>
+  <si>
+    <t>Episode 8, Reward: -51563, Makespan: 529.83h</t>
+  </si>
+  <si>
+    <t>Episode 9, Reward: -46353, Makespan: 512.58h</t>
+  </si>
+  <si>
+    <t>Episode 10, Reward: -47833, Makespan: 521.00h</t>
+  </si>
+  <si>
+    <t>Episode 11, Reward: -47793, Makespan: 532.83h</t>
+  </si>
+  <si>
+    <t>Episode 12, Reward: -68866, Makespan: 528.00h</t>
+  </si>
+  <si>
+    <t>Episode 13, Reward: -53141, Makespan: 513.58h</t>
+  </si>
+  <si>
+    <t>Episode 14, Reward: -51541, Makespan: 555.92h</t>
+  </si>
+  <si>
+    <t>Episode 15, Reward: -67208, Makespan: 527.25h</t>
+  </si>
+  <si>
+    <t>Episode 16, Reward: -44056, Makespan: 478.92h</t>
+  </si>
+  <si>
+    <t>Episode 17, Reward: -50063, Makespan: 520.67h</t>
+  </si>
+  <si>
+    <t>Episode 18, Reward: -65625, Makespan: 526.25h</t>
+  </si>
+  <si>
+    <t>Episode 19, Reward: -40338, Makespan: 478.92h</t>
+  </si>
+  <si>
+    <t>Episode 20, Reward: -60116, Makespan: 492.58h</t>
+  </si>
+  <si>
+    <t>Episode 21, Reward: -62038, Makespan: 508.25h</t>
+  </si>
+  <si>
+    <t>Episode 22, Reward: -56565, Makespan: 498.25h</t>
+  </si>
+  <si>
+    <t>Episode 23, Reward: -60470, Makespan: 501.58h</t>
+  </si>
+  <si>
+    <t>Episode 24, Reward: -56116, Makespan: 500.25h</t>
+  </si>
+  <si>
+    <t>Episode 25, Reward: -53576, Makespan: 535.58h</t>
+  </si>
+  <si>
+    <t>Episode 26, Reward: -58727, Makespan: 527.58h</t>
+  </si>
+  <si>
+    <t>Episode 27, Reward: -50358, Makespan: 527.58h</t>
+  </si>
+  <si>
+    <t>Episode 28, Reward: -51726, Makespan: 531.92h</t>
+  </si>
+  <si>
+    <t>Episode 29, Reward: -50345, Makespan: 530.58h</t>
+  </si>
+  <si>
+    <t>Episode 30, Reward: -51207, Makespan: 528.25h</t>
+  </si>
+  <si>
+    <t>Episode 31, Reward: -49558, Makespan: 527.58h</t>
+  </si>
+  <si>
+    <t>Episode 32, Reward: -50147, Makespan: 530.58h</t>
+  </si>
+  <si>
+    <t>Episode 33, Reward: -51025, Makespan: 531.58h</t>
+  </si>
+  <si>
+    <t>Episode 34, Reward: -84978, Makespan: 527.25h</t>
+  </si>
+  <si>
+    <t>Episode 35, Reward: -67326, Makespan: 527.25h</t>
+  </si>
+  <si>
+    <t>Episode 36, Reward: -51276, Makespan: 527.25h</t>
+  </si>
+  <si>
+    <t>Episode 37, Reward: -87773, Makespan: 556.50h</t>
+  </si>
+  <si>
+    <t>Episode 38, Reward: -84957, Makespan: 540.17h</t>
+  </si>
+  <si>
+    <t>Episode 39, Reward: -228247, Makespan: 883.72h</t>
+  </si>
+  <si>
+    <t>Episode 40, Reward: -300851, Makespan: 826.33h</t>
+  </si>
+  <si>
+    <t>Episode 41, Reward: -221396, Makespan: 811.33h</t>
+  </si>
+  <si>
+    <t>Episode 42, Reward: -179726, Makespan: 823.67h</t>
+  </si>
+  <si>
+    <t>Episode 43, Reward: -172596, Makespan: 811.33h</t>
+  </si>
+  <si>
+    <t>Episode 44, Reward: -221806, Makespan: 813.67h</t>
+  </si>
+  <si>
+    <t>Episode 45, Reward: -172611, Makespan: 811.33h</t>
+  </si>
+  <si>
+    <t>Episode 46, Reward: -223196, Makespan: 820.67h</t>
+  </si>
+  <si>
+    <t>Episode 47, Reward: -222986, Makespan: 813.67h</t>
+  </si>
+  <si>
+    <t>Episode 48, Reward: -240771, Makespan: 811.33h</t>
+  </si>
+  <si>
+    <t>Episode 49, Reward: -225356, Makespan: 813.67h</t>
+  </si>
+  <si>
+    <t>Episode 50, Reward: -172596, Makespan: 811.33h</t>
+  </si>
+  <si>
+    <t>Episode 51, Reward: -180416, Makespan: 811.33h</t>
+  </si>
+  <si>
+    <t>Episode 52, Reward: -220946, Makespan: 769.17h</t>
+  </si>
+  <si>
+    <t>Episode 53, Reward: -236495, Makespan: 797.85h</t>
+  </si>
+  <si>
+    <t>Episode 54, Reward: -144826, Makespan: 555.25h</t>
+  </si>
+  <si>
+    <t>Episode 55, Reward: -290754, Makespan: 791.92h</t>
+  </si>
+  <si>
+    <t>Episode 56, Reward: -99784, Makespan: 528.83h</t>
+  </si>
+  <si>
+    <t>Episode 57, Reward: -102271, Makespan: 531.67h</t>
+  </si>
+  <si>
+    <t>Episode 58, Reward: -259129, Makespan: 889.00h</t>
+  </si>
+  <si>
+    <t>Episode 59, Reward: -201754, Makespan: 876.17h</t>
+  </si>
+  <si>
+    <t>Episode 60, Reward: -200783, Makespan: 864.83h</t>
+  </si>
+  <si>
+    <t>Episode 61, Reward: -237463, Makespan: 872.17h</t>
+  </si>
+  <si>
+    <t>Episode 62, Reward: -201510, Makespan: 870.50h</t>
+  </si>
+  <si>
+    <t>Episode 63, Reward: -256827, Makespan: 870.50h</t>
+  </si>
+  <si>
+    <t>Episode 64, Reward: -208463, Makespan: 880.67h</t>
+  </si>
+  <si>
+    <t>Episode 65, Reward: -204802, Makespan: 878.67h</t>
+  </si>
+  <si>
+    <t>Episode 66, Reward: -206070, Makespan: 879.67h</t>
+  </si>
+  <si>
+    <t>Episode 67, Reward: -203433, Makespan: 865.67h</t>
+  </si>
+  <si>
+    <t>Episode 68, Reward: -216937, Makespan: 885.08h</t>
+  </si>
+  <si>
+    <t>Episode 69, Reward: -244520, Makespan: 884.17h</t>
+  </si>
+  <si>
+    <t>Episode 70, Reward: -260755, Makespan: 904.25h</t>
+  </si>
+  <si>
+    <t>Episode 71, Reward: -196434, Makespan: 869.50h</t>
+  </si>
+  <si>
+    <t>Episode 72, Reward: -357258, Makespan: 892.63h</t>
+  </si>
+  <si>
+    <t>Episode 73, Reward: -310454, Makespan: 873.33h</t>
+  </si>
+  <si>
+    <t>Episode 74, Reward: -243332, Makespan: 884.55h</t>
+  </si>
+  <si>
+    <t>Episode 75, Reward: -224849, Makespan: 846.83h</t>
+  </si>
+  <si>
+    <t>Episode 76, Reward: -194681, Makespan: 864.45h</t>
+  </si>
+  <si>
+    <t>Episode 77, Reward: -196954, Makespan: 642.25h</t>
+  </si>
+  <si>
+    <t>Episode 78, Reward: -179575, Makespan: 661.72h</t>
+  </si>
+  <si>
+    <t>Episode 79, Reward: -254513, Makespan: 873.25h</t>
+  </si>
+  <si>
+    <t>Episode 80, Reward: -331555, Makespan: 873.00h</t>
+  </si>
+  <si>
+    <t>Episode 81, Reward: -236226, Makespan: 739.50h</t>
+  </si>
+  <si>
+    <t>Episode 82, Reward: -208463, Makespan: 876.08h</t>
+  </si>
+  <si>
+    <t>Episode 83, Reward: -204383, Makespan: 862.67h</t>
+  </si>
+  <si>
+    <t>Episode 84, Reward: -288473, Makespan: 874.83h</t>
+  </si>
+  <si>
+    <t>Episode 85, Reward: -273865, Makespan: 864.33h</t>
+  </si>
+  <si>
+    <t>Episode 86, Reward: -244555, Makespan: 864.83h</t>
+  </si>
+  <si>
+    <t>Episode 87, Reward: -194730, Makespan: 862.00h</t>
+  </si>
+  <si>
+    <t>Episode 88, Reward: -199426, Makespan: 872.62h</t>
+  </si>
+  <si>
+    <t>Episode 89, Reward: -194098, Makespan: 865.50h</t>
+  </si>
+  <si>
+    <t>Episode 90, Reward: -302817, Makespan: 875.50h</t>
+  </si>
+  <si>
+    <t>Episode 91, Reward: -194309, Makespan: 866.25h</t>
+  </si>
+  <si>
+    <t>Episode 92, Reward: -241131, Makespan: 859.67h</t>
+  </si>
+  <si>
+    <t>Episode 93, Reward: -290274, Makespan: 859.67h</t>
+  </si>
+  <si>
+    <t>Episode 94, Reward: -104198, Makespan: 528.83h</t>
+  </si>
+  <si>
+    <t>Episode 95, Reward: -238144, Makespan: 871.33h</t>
+  </si>
+  <si>
+    <t>Episode 96, Reward: -244821, Makespan: 864.83h</t>
+  </si>
+  <si>
+    <t>Episode 97, Reward: -247269, Makespan: 664.83h</t>
+  </si>
+  <si>
+    <t>Episode 98, Reward: -212766, Makespan: 863.00h</t>
+  </si>
+  <si>
+    <t>Episode 99, Reward: -201909, Makespan: 877.50h</t>
+  </si>
+  <si>
+    <t>Episode 100, Reward: -215034, Makespan: 867.33h</t>
+  </si>
+  <si>
+    <t>Episode 101, Reward: -201025, Makespan: 865.22h</t>
+  </si>
+  <si>
+    <t>Episode 102, Reward: -232279, Makespan: 868.58h</t>
+  </si>
+  <si>
+    <t>Episode 103, Reward: -225891, Makespan: 652.67h</t>
+  </si>
+  <si>
+    <t>Episode 104, Reward: -214788, Makespan: 892.32h</t>
+  </si>
+  <si>
+    <t>Episode 105, Reward: -209179, Makespan: 883.33h</t>
+  </si>
+  <si>
+    <t>Episode 106, Reward: -195263, Makespan: 867.67h</t>
+  </si>
+  <si>
+    <t>Episode 107, Reward: -205529, Makespan: 873.33h</t>
+  </si>
+  <si>
+    <t>Episode 108, Reward: -210280, Makespan: 876.17h</t>
+  </si>
+  <si>
+    <t>Episode 109, Reward: -203325, Makespan: 880.58h</t>
+  </si>
+  <si>
+    <t>Episode 110, Reward: -200448, Makespan: 868.90h</t>
+  </si>
+  <si>
+    <t>Episode 111, Reward: -206270, Makespan: 878.67h</t>
+  </si>
+  <si>
+    <t>Episode 112, Reward: -277696, Makespan: 898.30h</t>
+  </si>
+  <si>
+    <t>Episode 113, Reward: -236820, Makespan: 658.83h</t>
+  </si>
+  <si>
+    <t>Episode 114, Reward: -177383, Makespan: 655.00h</t>
+  </si>
+  <si>
+    <t>Episode 115, Reward: -198604, Makespan: 861.50h</t>
+  </si>
+  <si>
+    <t>Episode 116, Reward: -199871, Makespan: 862.00h</t>
+  </si>
+  <si>
+    <t>Episode 117, Reward: -211484, Makespan: 887.60h</t>
+  </si>
+  <si>
+    <t>Episode 118, Reward: -210535, Makespan: 882.65h</t>
+  </si>
+  <si>
+    <t>Episode 119, Reward: -215627, Makespan: 895.03h</t>
+  </si>
+  <si>
+    <t>Episode 120, Reward: -211771, Makespan: 878.67h</t>
+  </si>
+  <si>
+    <t>Episode 121, Reward: -212801, Makespan: 878.67h</t>
+  </si>
+  <si>
+    <t>Episode 122, Reward: -203222, Makespan: 872.00h</t>
+  </si>
+  <si>
+    <t>Episode 123, Reward: -203718, Makespan: 870.50h</t>
+  </si>
+  <si>
+    <t>Episode 124, Reward: -207993, Makespan: 867.67h</t>
+  </si>
+  <si>
+    <t>Episode 125, Reward: -231552, Makespan: 867.67h</t>
+  </si>
+  <si>
+    <t>Episode 126, Reward: -155118, Makespan: 552.83h</t>
+  </si>
+  <si>
+    <t>Episode 127, Reward: -199896, Makespan: 877.67h</t>
+  </si>
+  <si>
+    <t>Episode 128, Reward: -194683, Makespan: 867.67h</t>
+  </si>
+  <si>
+    <t>Episode 129, Reward: -204530, Makespan: 873.33h</t>
+  </si>
+  <si>
+    <t>Episode 130, Reward: -200143, Makespan: 867.67h</t>
+  </si>
+  <si>
+    <t>Episode 131, Reward: -206728, Makespan: 867.67h</t>
+  </si>
+  <si>
+    <t>Episode 132, Reward: -252759, Makespan: 844.50h</t>
+  </si>
+  <si>
+    <t>Episode 133, Reward: -257863, Makespan: 669.67h</t>
+  </si>
+  <si>
+    <t>Episode 134, Reward: -205668, Makespan: 555.17h</t>
+  </si>
+  <si>
+    <t>Episode 135, Reward: -155956, Makespan: 654.33h</t>
+  </si>
+  <si>
+    <t>Episode 136, Reward: -158486, Makespan: 648.33h</t>
+  </si>
+  <si>
+    <t>Episode 137, Reward: -232776, Makespan: 880.02h</t>
+  </si>
+  <si>
+    <t>Episode 138, Reward: -178235, Makespan: 706.92h</t>
+  </si>
+  <si>
+    <t>Episode 139, Reward: -176379, Makespan: 705.08h</t>
+  </si>
+  <si>
+    <t>Episode 140, Reward: -218316, Makespan: 880.25h</t>
+  </si>
+  <si>
+    <t>Episode 141, Reward: -208807, Makespan: 869.17h</t>
+  </si>
+  <si>
+    <t>Episode 142, Reward: -207216, Makespan: 854.00h</t>
+  </si>
+  <si>
+    <t>Episode 143, Reward: -172914, Makespan: 737.17h</t>
+  </si>
+  <si>
+    <t>Episode 144, Reward: -179803, Makespan: 737.17h</t>
+  </si>
+  <si>
+    <t>Episode 145, Reward: -170064, Makespan: 737.17h</t>
+  </si>
+  <si>
+    <t>Episode 146, Reward: -169622, Makespan: 737.17h</t>
+  </si>
+  <si>
+    <t>Episode 147, Reward: -172000, Makespan: 737.17h</t>
+  </si>
+  <si>
+    <t>Episode 148, Reward: -168404, Makespan: 737.17h</t>
+  </si>
+  <si>
+    <t>Episode 149, Reward: -157231, Makespan: 740.50h</t>
+  </si>
+  <si>
+    <t>Episode 150, Reward: -208914, Makespan: 869.92h</t>
+  </si>
+  <si>
+    <t>Episode 151, Reward: -220785, Makespan: 866.58h</t>
+  </si>
+  <si>
+    <t>Episode 152, Reward: -219720, Makespan: 885.90h</t>
+  </si>
+  <si>
+    <t>Episode 153, Reward: -192423, Makespan: 855.00h</t>
+  </si>
+  <si>
+    <t>Episode 154, Reward: -201663, Makespan: 856.33h</t>
+  </si>
+  <si>
+    <t>Episode 155, Reward: -160580, Makespan: 593.58h</t>
+  </si>
+  <si>
+    <t>Episode 156, Reward: -201756, Makespan: 845.67h</t>
+  </si>
+  <si>
+    <t>Episode 157, Reward: -171931, Makespan: 770.83h</t>
+  </si>
+  <si>
+    <t>Episode 158, Reward: -167782, Makespan: 760.67h</t>
   </si>
 </sst>
 </file>
@@ -2457,2310 +2931,483 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$1:$B$767</c:f>
+              <c:f>Sheet1!$E$1:$E$158</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="767"/>
+                <c:ptCount val="158"/>
                 <c:pt idx="0">
-                  <c:v>-102668</c:v>
+                  <c:v>888.37</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-47778</c:v>
+                  <c:v>665.83</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-48999</c:v>
+                  <c:v>528.83000000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-75036</c:v>
+                  <c:v>528.83000000000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-33940</c:v>
+                  <c:v>528.83000000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-49695</c:v>
+                  <c:v>528.83000000000004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-55880</c:v>
+                  <c:v>528.83000000000004</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-146151</c:v>
+                  <c:v>529.83000000000004</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-169400</c:v>
+                  <c:v>512.58000000000004</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-111323</c:v>
+                  <c:v>521</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-105113</c:v>
+                  <c:v>532.83000000000004</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-52333</c:v>
+                  <c:v>528</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-114240</c:v>
+                  <c:v>513.58000000000004</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-100915</c:v>
+                  <c:v>555.91999999999996</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-98380</c:v>
+                  <c:v>527.25</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-67350</c:v>
+                  <c:v>478.92</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-66530</c:v>
+                  <c:v>520.66999999999996</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-119145</c:v>
+                  <c:v>526.25</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-369490</c:v>
+                  <c:v>478.92</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-375488</c:v>
+                  <c:v>492.58</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-152336</c:v>
+                  <c:v>508.25</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-152216</c:v>
+                  <c:v>498.25</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-152216</c:v>
+                  <c:v>501.58</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-152216</c:v>
+                  <c:v>500.25</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-149366</c:v>
+                  <c:v>535.58000000000004</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-62022</c:v>
+                  <c:v>527.58000000000004</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-62013</c:v>
+                  <c:v>527.58000000000004</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-63043</c:v>
+                  <c:v>531.91999999999996</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-62013</c:v>
+                  <c:v>530.58000000000004</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-62013</c:v>
+                  <c:v>528.25</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-62013</c:v>
+                  <c:v>527.58000000000004</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-62013</c:v>
+                  <c:v>530.58000000000004</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-62623</c:v>
+                  <c:v>531.58000000000004</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-62188</c:v>
+                  <c:v>527.25</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-62013</c:v>
+                  <c:v>527.25</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-62013</c:v>
+                  <c:v>527.25</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-62013</c:v>
+                  <c:v>556.5</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-62013</c:v>
+                  <c:v>540.16999999999996</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-62013</c:v>
+                  <c:v>883.72</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-62013</c:v>
+                  <c:v>826.33</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-62013</c:v>
+                  <c:v>811.33</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-62013</c:v>
+                  <c:v>823.67</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-62013</c:v>
+                  <c:v>811.33</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-62013</c:v>
+                  <c:v>813.67</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-62013</c:v>
+                  <c:v>811.33</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-62013</c:v>
+                  <c:v>820.67</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-62013</c:v>
+                  <c:v>813.67</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-62013</c:v>
+                  <c:v>811.33</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-62013</c:v>
+                  <c:v>813.67</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>-60663</c:v>
+                  <c:v>811.33</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>-61779</c:v>
+                  <c:v>811.33</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>-61935</c:v>
+                  <c:v>769.17</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>-62013</c:v>
+                  <c:v>797.85</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>-62013</c:v>
+                  <c:v>555.25</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>-62013</c:v>
+                  <c:v>791.92</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>-62013</c:v>
+                  <c:v>528.83000000000004</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>-62013</c:v>
+                  <c:v>531.66999999999996</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>-62013</c:v>
+                  <c:v>889</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>-62013</c:v>
+                  <c:v>876.17</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>-62013</c:v>
+                  <c:v>864.83</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>-63422</c:v>
+                  <c:v>872.17</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>-68603</c:v>
+                  <c:v>870.5</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>-62013</c:v>
+                  <c:v>870.5</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>-62013</c:v>
+                  <c:v>880.67</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>-62013</c:v>
+                  <c:v>878.67</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>-62013</c:v>
+                  <c:v>879.67</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>-62013</c:v>
+                  <c:v>865.67</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>-62013</c:v>
+                  <c:v>885.08</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>-62013</c:v>
+                  <c:v>884.17</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>-62013</c:v>
+                  <c:v>904.25</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>-62013</c:v>
+                  <c:v>869.5</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>-61853</c:v>
+                  <c:v>892.63</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>-62133</c:v>
+                  <c:v>873.33</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>-62013</c:v>
+                  <c:v>884.55</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>-62013</c:v>
+                  <c:v>846.83</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>-114173</c:v>
+                  <c:v>864.45</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>-194909</c:v>
+                  <c:v>642.25</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>-121118</c:v>
+                  <c:v>661.72</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>-91716</c:v>
+                  <c:v>873.25</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>-95531</c:v>
+                  <c:v>873</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>-144210</c:v>
+                  <c:v>739.5</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>-61366</c:v>
+                  <c:v>876.08</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>-79363</c:v>
+                  <c:v>862.67</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>-92303</c:v>
+                  <c:v>874.83</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>-62100</c:v>
+                  <c:v>864.33</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>-37518</c:v>
+                  <c:v>864.83</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>-24898</c:v>
+                  <c:v>862</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>-64572</c:v>
+                  <c:v>872.62</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>-75174</c:v>
+                  <c:v>865.5</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>-19923</c:v>
+                  <c:v>875.5</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>-54694</c:v>
+                  <c:v>866.25</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>-67323</c:v>
+                  <c:v>859.67</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>-75941</c:v>
+                  <c:v>859.67</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>-32440</c:v>
+                  <c:v>528.83000000000004</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>-66007</c:v>
+                  <c:v>871.33</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>-79504</c:v>
+                  <c:v>864.83</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>-25843</c:v>
+                  <c:v>664.83</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>-25723</c:v>
+                  <c:v>863</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>-25723</c:v>
+                  <c:v>877.5</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>-25723</c:v>
+                  <c:v>867.33</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>-25723</c:v>
+                  <c:v>865.22</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>-25723</c:v>
+                  <c:v>868.58</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>-25723</c:v>
+                  <c:v>652.66999999999996</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>-25723</c:v>
+                  <c:v>892.32</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>-25723</c:v>
+                  <c:v>883.33</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>-25723</c:v>
+                  <c:v>867.67</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>-25723</c:v>
+                  <c:v>873.33</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>-27947</c:v>
+                  <c:v>876.17</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>-50259</c:v>
+                  <c:v>880.58</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>-42419</c:v>
+                  <c:v>868.9</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>-38669</c:v>
+                  <c:v>878.67</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>-43949</c:v>
+                  <c:v>898.3</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>-53356</c:v>
+                  <c:v>658.83</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>-82092</c:v>
+                  <c:v>655</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>-77645</c:v>
+                  <c:v>861.5</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>-33029</c:v>
+                  <c:v>862</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>-67099</c:v>
+                  <c:v>887.6</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>-71484</c:v>
+                  <c:v>882.65</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>-56424</c:v>
+                  <c:v>895.03</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>-56433</c:v>
+                  <c:v>878.67</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>-55444</c:v>
+                  <c:v>878.67</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>-70568</c:v>
+                  <c:v>872</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>-55907</c:v>
+                  <c:v>870.5</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>-70062</c:v>
+                  <c:v>867.67</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>-55836</c:v>
+                  <c:v>867.67</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>-60189</c:v>
+                  <c:v>552.83000000000004</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>-100259</c:v>
+                  <c:v>877.67</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>-63723</c:v>
+                  <c:v>867.67</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>-64978</c:v>
+                  <c:v>873.33</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>-63661</c:v>
+                  <c:v>867.67</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>-69954</c:v>
+                  <c:v>867.67</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>-64978</c:v>
+                  <c:v>844.5</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>-69824</c:v>
+                  <c:v>669.67</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>-104085</c:v>
+                  <c:v>555.16999999999996</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>-58706</c:v>
+                  <c:v>654.33000000000004</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>-61958</c:v>
+                  <c:v>648.33000000000004</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>-81998</c:v>
+                  <c:v>880.02</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>-56018</c:v>
+                  <c:v>706.92</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>-56266</c:v>
+                  <c:v>705.08</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>-56553</c:v>
+                  <c:v>880.25</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>-67524</c:v>
+                  <c:v>869.17</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>-56138</c:v>
+                  <c:v>854</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>-91139</c:v>
+                  <c:v>737.17</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>-87738</c:v>
+                  <c:v>737.17</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>-87718</c:v>
+                  <c:v>737.17</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>-87638</c:v>
+                  <c:v>737.17</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>-87638</c:v>
+                  <c:v>737.17</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>-84768</c:v>
+                  <c:v>737.17</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>-68098</c:v>
+                  <c:v>740.5</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>-68128</c:v>
+                  <c:v>869.92</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>-88368</c:v>
+                  <c:v>866.58</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>-125516</c:v>
+                  <c:v>885.9</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>-89523</c:v>
+                  <c:v>855</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>-86431</c:v>
+                  <c:v>856.33</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>-69350</c:v>
+                  <c:v>593.58000000000004</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>-72928</c:v>
+                  <c:v>845.67</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>-86128</c:v>
+                  <c:v>770.83</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>-87266</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>-83644</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>-83707</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>-80483</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>-83858</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>-83319</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>-84357</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>-109227</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>-85529</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>-87098</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>-126252</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>-85066</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>-111443</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>-84013</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>-85403</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>-86629</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>-83439</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>-86213</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>-86308</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>-87863</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>-93771</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>-89121</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>-114711</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>-96705</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>-100500</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>-95433</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>-93787</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>-89626</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>-99499</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>-84302</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>-81284</c:v>
-                </c:pt>
-                <c:pt idx="188">
-                  <c:v>-78976</c:v>
-                </c:pt>
-                <c:pt idx="189">
-                  <c:v>-98388</c:v>
-                </c:pt>
-                <c:pt idx="190">
-                  <c:v>-92813</c:v>
-                </c:pt>
-                <c:pt idx="191">
-                  <c:v>-140902</c:v>
-                </c:pt>
-                <c:pt idx="192">
-                  <c:v>-134064</c:v>
-                </c:pt>
-                <c:pt idx="193">
-                  <c:v>-127408</c:v>
-                </c:pt>
-                <c:pt idx="194">
-                  <c:v>-136333</c:v>
-                </c:pt>
-                <c:pt idx="195">
-                  <c:v>-126656</c:v>
-                </c:pt>
-                <c:pt idx="196">
-                  <c:v>-122095</c:v>
-                </c:pt>
-                <c:pt idx="197">
-                  <c:v>-114296</c:v>
-                </c:pt>
-                <c:pt idx="198">
-                  <c:v>-123543</c:v>
-                </c:pt>
-                <c:pt idx="199">
-                  <c:v>-87070</c:v>
-                </c:pt>
-                <c:pt idx="200">
-                  <c:v>-126086</c:v>
-                </c:pt>
-                <c:pt idx="201">
-                  <c:v>-107630</c:v>
-                </c:pt>
-                <c:pt idx="202">
-                  <c:v>-96461</c:v>
-                </c:pt>
-                <c:pt idx="203">
-                  <c:v>-111667</c:v>
-                </c:pt>
-                <c:pt idx="204">
-                  <c:v>-69789</c:v>
-                </c:pt>
-                <c:pt idx="205">
-                  <c:v>-77454</c:v>
-                </c:pt>
-                <c:pt idx="206">
-                  <c:v>-77524</c:v>
-                </c:pt>
-                <c:pt idx="207">
-                  <c:v>-75020</c:v>
-                </c:pt>
-                <c:pt idx="208">
-                  <c:v>-115177</c:v>
-                </c:pt>
-                <c:pt idx="209">
-                  <c:v>-125997</c:v>
-                </c:pt>
-                <c:pt idx="210">
-                  <c:v>-88441</c:v>
-                </c:pt>
-                <c:pt idx="211">
-                  <c:v>-123215</c:v>
-                </c:pt>
-                <c:pt idx="212">
-                  <c:v>-94326</c:v>
-                </c:pt>
-                <c:pt idx="213">
-                  <c:v>-129165</c:v>
-                </c:pt>
-                <c:pt idx="214">
-                  <c:v>-131758</c:v>
-                </c:pt>
-                <c:pt idx="215">
-                  <c:v>-143882</c:v>
-                </c:pt>
-                <c:pt idx="216">
-                  <c:v>-120647</c:v>
-                </c:pt>
-                <c:pt idx="217">
-                  <c:v>-113365</c:v>
-                </c:pt>
-                <c:pt idx="218">
-                  <c:v>-175047</c:v>
-                </c:pt>
-                <c:pt idx="219">
-                  <c:v>-102115</c:v>
-                </c:pt>
-                <c:pt idx="220">
-                  <c:v>-125117</c:v>
-                </c:pt>
-                <c:pt idx="221">
-                  <c:v>-126398</c:v>
-                </c:pt>
-                <c:pt idx="222">
-                  <c:v>-133814</c:v>
-                </c:pt>
-                <c:pt idx="223">
-                  <c:v>-186442</c:v>
-                </c:pt>
-                <c:pt idx="224">
-                  <c:v>-154148</c:v>
-                </c:pt>
-                <c:pt idx="225">
-                  <c:v>-109719</c:v>
-                </c:pt>
-                <c:pt idx="226">
-                  <c:v>-95398</c:v>
-                </c:pt>
-                <c:pt idx="227">
-                  <c:v>-73502</c:v>
-                </c:pt>
-                <c:pt idx="228">
-                  <c:v>-194601</c:v>
-                </c:pt>
-                <c:pt idx="229">
-                  <c:v>-64873</c:v>
-                </c:pt>
-                <c:pt idx="230">
-                  <c:v>-74336</c:v>
-                </c:pt>
-                <c:pt idx="231">
-                  <c:v>-61515</c:v>
-                </c:pt>
-                <c:pt idx="232">
-                  <c:v>-85859</c:v>
-                </c:pt>
-                <c:pt idx="233">
-                  <c:v>-57532</c:v>
-                </c:pt>
-                <c:pt idx="234">
-                  <c:v>-40801</c:v>
-                </c:pt>
-                <c:pt idx="235">
-                  <c:v>-114230</c:v>
-                </c:pt>
-                <c:pt idx="236">
-                  <c:v>-99408</c:v>
-                </c:pt>
-                <c:pt idx="237">
-                  <c:v>-103679</c:v>
-                </c:pt>
-                <c:pt idx="238">
-                  <c:v>-112464</c:v>
-                </c:pt>
-                <c:pt idx="239">
-                  <c:v>-162897</c:v>
-                </c:pt>
-                <c:pt idx="240">
-                  <c:v>-129601</c:v>
-                </c:pt>
-                <c:pt idx="241">
-                  <c:v>-98879</c:v>
-                </c:pt>
-                <c:pt idx="242">
-                  <c:v>-60420</c:v>
-                </c:pt>
-                <c:pt idx="243">
-                  <c:v>-96427</c:v>
-                </c:pt>
-                <c:pt idx="244">
-                  <c:v>-108606</c:v>
-                </c:pt>
-                <c:pt idx="245">
-                  <c:v>-94722</c:v>
-                </c:pt>
-                <c:pt idx="246">
-                  <c:v>-71896</c:v>
-                </c:pt>
-                <c:pt idx="247">
-                  <c:v>-49199</c:v>
-                </c:pt>
-                <c:pt idx="248">
-                  <c:v>-59506</c:v>
-                </c:pt>
-                <c:pt idx="249">
-                  <c:v>-73400</c:v>
-                </c:pt>
-                <c:pt idx="250">
-                  <c:v>-54910</c:v>
-                </c:pt>
-                <c:pt idx="251">
-                  <c:v>-49838</c:v>
-                </c:pt>
-                <c:pt idx="252">
-                  <c:v>-53196</c:v>
-                </c:pt>
-                <c:pt idx="253">
-                  <c:v>-51370</c:v>
-                </c:pt>
-                <c:pt idx="254">
-                  <c:v>-51635</c:v>
-                </c:pt>
-                <c:pt idx="255">
-                  <c:v>-121401</c:v>
-                </c:pt>
-                <c:pt idx="256">
-                  <c:v>-162371</c:v>
-                </c:pt>
-                <c:pt idx="257">
-                  <c:v>-72156</c:v>
-                </c:pt>
-                <c:pt idx="258">
-                  <c:v>-132362</c:v>
-                </c:pt>
-                <c:pt idx="259">
-                  <c:v>-59040</c:v>
-                </c:pt>
-                <c:pt idx="260">
-                  <c:v>-69536</c:v>
-                </c:pt>
-                <c:pt idx="261">
-                  <c:v>-70008</c:v>
-                </c:pt>
-                <c:pt idx="262">
-                  <c:v>-88009</c:v>
-                </c:pt>
-                <c:pt idx="263">
-                  <c:v>-119809</c:v>
-                </c:pt>
-                <c:pt idx="264">
-                  <c:v>-57058</c:v>
-                </c:pt>
-                <c:pt idx="265">
-                  <c:v>-57856</c:v>
-                </c:pt>
-                <c:pt idx="266">
-                  <c:v>-139146</c:v>
-                </c:pt>
-                <c:pt idx="267">
-                  <c:v>-181050</c:v>
-                </c:pt>
-                <c:pt idx="268">
-                  <c:v>-155273</c:v>
-                </c:pt>
-                <c:pt idx="269">
-                  <c:v>-85371</c:v>
-                </c:pt>
-                <c:pt idx="270">
-                  <c:v>-56244</c:v>
-                </c:pt>
-                <c:pt idx="271">
-                  <c:v>-124021</c:v>
-                </c:pt>
-                <c:pt idx="272">
-                  <c:v>-102564</c:v>
-                </c:pt>
-                <c:pt idx="273">
-                  <c:v>-62899</c:v>
-                </c:pt>
-                <c:pt idx="274">
-                  <c:v>-119807</c:v>
-                </c:pt>
-                <c:pt idx="275">
-                  <c:v>-88084</c:v>
-                </c:pt>
-                <c:pt idx="276">
-                  <c:v>-71488</c:v>
-                </c:pt>
-                <c:pt idx="277">
-                  <c:v>-56612</c:v>
-                </c:pt>
-                <c:pt idx="278">
-                  <c:v>-64827</c:v>
-                </c:pt>
-                <c:pt idx="279">
-                  <c:v>-50619</c:v>
-                </c:pt>
-                <c:pt idx="280">
-                  <c:v>-96774</c:v>
-                </c:pt>
-                <c:pt idx="281">
-                  <c:v>-73800</c:v>
-                </c:pt>
-                <c:pt idx="282">
-                  <c:v>-83517</c:v>
-                </c:pt>
-                <c:pt idx="283">
-                  <c:v>-96331</c:v>
-                </c:pt>
-                <c:pt idx="284">
-                  <c:v>-66642</c:v>
-                </c:pt>
-                <c:pt idx="285">
-                  <c:v>-103972</c:v>
-                </c:pt>
-                <c:pt idx="286">
-                  <c:v>-83302</c:v>
-                </c:pt>
-                <c:pt idx="287">
-                  <c:v>-77122</c:v>
-                </c:pt>
-                <c:pt idx="288">
-                  <c:v>-80916</c:v>
-                </c:pt>
-                <c:pt idx="289">
-                  <c:v>-76939</c:v>
-                </c:pt>
-                <c:pt idx="290">
-                  <c:v>-109256</c:v>
-                </c:pt>
-                <c:pt idx="291">
-                  <c:v>-81589</c:v>
-                </c:pt>
-                <c:pt idx="292">
-                  <c:v>-82489</c:v>
-                </c:pt>
-                <c:pt idx="293">
-                  <c:v>-151494</c:v>
-                </c:pt>
-                <c:pt idx="294">
-                  <c:v>-111039</c:v>
-                </c:pt>
-                <c:pt idx="295">
-                  <c:v>-81746</c:v>
-                </c:pt>
-                <c:pt idx="296">
-                  <c:v>-85684</c:v>
-                </c:pt>
-                <c:pt idx="297">
-                  <c:v>-85468</c:v>
-                </c:pt>
-                <c:pt idx="298">
-                  <c:v>-77407</c:v>
-                </c:pt>
-                <c:pt idx="299">
-                  <c:v>-69936</c:v>
-                </c:pt>
-                <c:pt idx="300">
-                  <c:v>-66717</c:v>
-                </c:pt>
-                <c:pt idx="301">
-                  <c:v>-68494</c:v>
-                </c:pt>
-                <c:pt idx="302">
-                  <c:v>-69819</c:v>
-                </c:pt>
-                <c:pt idx="303">
-                  <c:v>-68409</c:v>
-                </c:pt>
-                <c:pt idx="304">
-                  <c:v>-69496</c:v>
-                </c:pt>
-                <c:pt idx="305">
-                  <c:v>-71456</c:v>
-                </c:pt>
-                <c:pt idx="306">
-                  <c:v>-73589</c:v>
-                </c:pt>
-                <c:pt idx="307">
-                  <c:v>-76071</c:v>
-                </c:pt>
-                <c:pt idx="308">
-                  <c:v>-94129</c:v>
-                </c:pt>
-                <c:pt idx="309">
-                  <c:v>-81142</c:v>
-                </c:pt>
-                <c:pt idx="310">
-                  <c:v>-98789</c:v>
-                </c:pt>
-                <c:pt idx="311">
-                  <c:v>-84906</c:v>
-                </c:pt>
-                <c:pt idx="312">
-                  <c:v>-88704</c:v>
-                </c:pt>
-                <c:pt idx="313">
-                  <c:v>-142799</c:v>
-                </c:pt>
-                <c:pt idx="314">
-                  <c:v>-117981</c:v>
-                </c:pt>
-                <c:pt idx="315">
-                  <c:v>-84286</c:v>
-                </c:pt>
-                <c:pt idx="316">
-                  <c:v>-110878</c:v>
-                </c:pt>
-                <c:pt idx="317">
-                  <c:v>-102437</c:v>
-                </c:pt>
-                <c:pt idx="318">
-                  <c:v>-82309</c:v>
-                </c:pt>
-                <c:pt idx="319">
-                  <c:v>-82772</c:v>
-                </c:pt>
-                <c:pt idx="320">
-                  <c:v>-82413</c:v>
-                </c:pt>
-                <c:pt idx="321">
-                  <c:v>-95458</c:v>
-                </c:pt>
-                <c:pt idx="322">
-                  <c:v>-82369</c:v>
-                </c:pt>
-                <c:pt idx="323">
-                  <c:v>-82369</c:v>
-                </c:pt>
-                <c:pt idx="324">
-                  <c:v>-82369</c:v>
-                </c:pt>
-                <c:pt idx="325">
-                  <c:v>-94174</c:v>
-                </c:pt>
-                <c:pt idx="326">
-                  <c:v>-117149</c:v>
-                </c:pt>
-                <c:pt idx="327">
-                  <c:v>-98724</c:v>
-                </c:pt>
-                <c:pt idx="328">
-                  <c:v>-106195</c:v>
-                </c:pt>
-                <c:pt idx="329">
-                  <c:v>-83689</c:v>
-                </c:pt>
-                <c:pt idx="330">
-                  <c:v>-124597</c:v>
-                </c:pt>
-                <c:pt idx="331">
-                  <c:v>-84943</c:v>
-                </c:pt>
-                <c:pt idx="332">
-                  <c:v>-101144</c:v>
-                </c:pt>
-                <c:pt idx="333">
-                  <c:v>-63602</c:v>
-                </c:pt>
-                <c:pt idx="334">
-                  <c:v>-69530</c:v>
-                </c:pt>
-                <c:pt idx="335">
-                  <c:v>-87875</c:v>
-                </c:pt>
-                <c:pt idx="336">
-                  <c:v>-99593</c:v>
-                </c:pt>
-                <c:pt idx="337">
-                  <c:v>-98918</c:v>
-                </c:pt>
-                <c:pt idx="338">
-                  <c:v>-93844</c:v>
-                </c:pt>
-                <c:pt idx="339">
-                  <c:v>-85119</c:v>
-                </c:pt>
-                <c:pt idx="340">
-                  <c:v>-75438</c:v>
-                </c:pt>
-                <c:pt idx="341">
-                  <c:v>-77822</c:v>
-                </c:pt>
-                <c:pt idx="342">
-                  <c:v>-64273</c:v>
-                </c:pt>
-                <c:pt idx="343">
-                  <c:v>-67630</c:v>
-                </c:pt>
-                <c:pt idx="344">
-                  <c:v>-80602</c:v>
-                </c:pt>
-                <c:pt idx="345">
-                  <c:v>-65355</c:v>
-                </c:pt>
-                <c:pt idx="346">
-                  <c:v>-101931</c:v>
-                </c:pt>
-                <c:pt idx="347">
-                  <c:v>-65439</c:v>
-                </c:pt>
-                <c:pt idx="348">
-                  <c:v>-62681</c:v>
-                </c:pt>
-                <c:pt idx="349">
-                  <c:v>-69339</c:v>
-                </c:pt>
-                <c:pt idx="350">
-                  <c:v>-61519</c:v>
-                </c:pt>
-                <c:pt idx="351">
-                  <c:v>-126892</c:v>
-                </c:pt>
-                <c:pt idx="352">
-                  <c:v>-103045</c:v>
-                </c:pt>
-                <c:pt idx="353">
-                  <c:v>-69560</c:v>
-                </c:pt>
-                <c:pt idx="354">
-                  <c:v>-81225</c:v>
-                </c:pt>
-                <c:pt idx="355">
-                  <c:v>-112956</c:v>
-                </c:pt>
-                <c:pt idx="356">
-                  <c:v>-146735</c:v>
-                </c:pt>
-                <c:pt idx="357">
-                  <c:v>-105794</c:v>
-                </c:pt>
-                <c:pt idx="358">
-                  <c:v>-91585</c:v>
-                </c:pt>
-                <c:pt idx="359">
-                  <c:v>-97264</c:v>
-                </c:pt>
-                <c:pt idx="360">
-                  <c:v>-88603</c:v>
-                </c:pt>
-                <c:pt idx="361">
-                  <c:v>-75504</c:v>
-                </c:pt>
-                <c:pt idx="362">
-                  <c:v>-101490</c:v>
-                </c:pt>
-                <c:pt idx="363">
-                  <c:v>-75563</c:v>
-                </c:pt>
-                <c:pt idx="364">
-                  <c:v>-85686</c:v>
-                </c:pt>
-                <c:pt idx="365">
-                  <c:v>-103419</c:v>
-                </c:pt>
-                <c:pt idx="366">
-                  <c:v>-107314</c:v>
-                </c:pt>
-                <c:pt idx="367">
-                  <c:v>-105103</c:v>
-                </c:pt>
-                <c:pt idx="368">
-                  <c:v>-88048</c:v>
-                </c:pt>
-                <c:pt idx="369">
-                  <c:v>-81135</c:v>
-                </c:pt>
-                <c:pt idx="370">
-                  <c:v>-70004</c:v>
-                </c:pt>
-                <c:pt idx="371">
-                  <c:v>-93019</c:v>
-                </c:pt>
-                <c:pt idx="372">
-                  <c:v>-104065</c:v>
-                </c:pt>
-                <c:pt idx="373">
-                  <c:v>-76269</c:v>
-                </c:pt>
-                <c:pt idx="374">
-                  <c:v>-63752</c:v>
-                </c:pt>
-                <c:pt idx="375">
-                  <c:v>-77086</c:v>
-                </c:pt>
-                <c:pt idx="376">
-                  <c:v>-63296</c:v>
-                </c:pt>
-                <c:pt idx="377">
-                  <c:v>-71661</c:v>
-                </c:pt>
-                <c:pt idx="378">
-                  <c:v>-109005</c:v>
-                </c:pt>
-                <c:pt idx="379">
-                  <c:v>-65444</c:v>
-                </c:pt>
-                <c:pt idx="380">
-                  <c:v>-63224</c:v>
-                </c:pt>
-                <c:pt idx="381">
-                  <c:v>-86046</c:v>
-                </c:pt>
-                <c:pt idx="382">
-                  <c:v>-96059</c:v>
-                </c:pt>
-                <c:pt idx="383">
-                  <c:v>-97338</c:v>
-                </c:pt>
-                <c:pt idx="384">
-                  <c:v>-94409</c:v>
-                </c:pt>
-                <c:pt idx="385">
-                  <c:v>-94409</c:v>
-                </c:pt>
-                <c:pt idx="386">
-                  <c:v>-95490</c:v>
-                </c:pt>
-                <c:pt idx="387">
-                  <c:v>-95263</c:v>
-                </c:pt>
-                <c:pt idx="388">
-                  <c:v>-119724</c:v>
-                </c:pt>
-                <c:pt idx="389">
-                  <c:v>-65429</c:v>
-                </c:pt>
-                <c:pt idx="390">
-                  <c:v>-70879</c:v>
-                </c:pt>
-                <c:pt idx="391">
-                  <c:v>-92409</c:v>
-                </c:pt>
-                <c:pt idx="392">
-                  <c:v>-119658</c:v>
-                </c:pt>
-                <c:pt idx="393">
-                  <c:v>-90059</c:v>
-                </c:pt>
-                <c:pt idx="394">
-                  <c:v>-90849</c:v>
-                </c:pt>
-                <c:pt idx="395">
-                  <c:v>-78314</c:v>
-                </c:pt>
-                <c:pt idx="396">
-                  <c:v>-129784</c:v>
-                </c:pt>
-                <c:pt idx="397">
-                  <c:v>-112439</c:v>
-                </c:pt>
-                <c:pt idx="398">
-                  <c:v>-107456</c:v>
-                </c:pt>
-                <c:pt idx="399">
-                  <c:v>-104901</c:v>
-                </c:pt>
-                <c:pt idx="400">
-                  <c:v>-102500</c:v>
-                </c:pt>
-                <c:pt idx="401">
-                  <c:v>-84436</c:v>
-                </c:pt>
-                <c:pt idx="402">
-                  <c:v>-114806</c:v>
-                </c:pt>
-                <c:pt idx="403">
-                  <c:v>-122436</c:v>
-                </c:pt>
-                <c:pt idx="404">
-                  <c:v>-101649</c:v>
-                </c:pt>
-                <c:pt idx="405">
-                  <c:v>-105819</c:v>
-                </c:pt>
-                <c:pt idx="406">
-                  <c:v>-112388</c:v>
-                </c:pt>
-                <c:pt idx="407">
-                  <c:v>-155217</c:v>
-                </c:pt>
-                <c:pt idx="408">
-                  <c:v>-117406</c:v>
-                </c:pt>
-                <c:pt idx="409">
-                  <c:v>-138609</c:v>
-                </c:pt>
-                <c:pt idx="410">
-                  <c:v>-105199</c:v>
-                </c:pt>
-                <c:pt idx="411">
-                  <c:v>-129817</c:v>
-                </c:pt>
-                <c:pt idx="412">
-                  <c:v>-142191</c:v>
-                </c:pt>
-                <c:pt idx="413">
-                  <c:v>-131704</c:v>
-                </c:pt>
-                <c:pt idx="414">
-                  <c:v>-75103</c:v>
-                </c:pt>
-                <c:pt idx="415">
-                  <c:v>-102668</c:v>
-                </c:pt>
-                <c:pt idx="416">
-                  <c:v>-73729</c:v>
-                </c:pt>
-                <c:pt idx="417">
-                  <c:v>-74737</c:v>
-                </c:pt>
-                <c:pt idx="418">
-                  <c:v>-73350</c:v>
-                </c:pt>
-                <c:pt idx="419">
-                  <c:v>-73391</c:v>
-                </c:pt>
-                <c:pt idx="420">
-                  <c:v>-74067</c:v>
-                </c:pt>
-                <c:pt idx="421">
-                  <c:v>-75733</c:v>
-                </c:pt>
-                <c:pt idx="422">
-                  <c:v>-114243</c:v>
-                </c:pt>
-                <c:pt idx="423">
-                  <c:v>-100983</c:v>
-                </c:pt>
-                <c:pt idx="424">
-                  <c:v>-66799</c:v>
-                </c:pt>
-                <c:pt idx="425">
-                  <c:v>-131367</c:v>
-                </c:pt>
-                <c:pt idx="426">
-                  <c:v>-93018</c:v>
-                </c:pt>
-                <c:pt idx="427">
-                  <c:v>-134939</c:v>
-                </c:pt>
-                <c:pt idx="428">
-                  <c:v>-98536</c:v>
-                </c:pt>
-                <c:pt idx="429">
-                  <c:v>-72587</c:v>
-                </c:pt>
-                <c:pt idx="430">
-                  <c:v>-63848</c:v>
-                </c:pt>
-                <c:pt idx="431">
-                  <c:v>-74494</c:v>
-                </c:pt>
-                <c:pt idx="432">
-                  <c:v>-87405</c:v>
-                </c:pt>
-                <c:pt idx="433">
-                  <c:v>-89934</c:v>
-                </c:pt>
-                <c:pt idx="434">
-                  <c:v>-86808</c:v>
-                </c:pt>
-                <c:pt idx="435">
-                  <c:v>-128435</c:v>
-                </c:pt>
-                <c:pt idx="436">
-                  <c:v>-104711</c:v>
-                </c:pt>
-                <c:pt idx="437">
-                  <c:v>-112420</c:v>
-                </c:pt>
-                <c:pt idx="438">
-                  <c:v>-117794</c:v>
-                </c:pt>
-                <c:pt idx="439">
-                  <c:v>-117910</c:v>
-                </c:pt>
-                <c:pt idx="440">
-                  <c:v>-134196</c:v>
-                </c:pt>
-                <c:pt idx="441">
-                  <c:v>-111638</c:v>
-                </c:pt>
-                <c:pt idx="442">
-                  <c:v>-114109</c:v>
-                </c:pt>
-                <c:pt idx="443">
-                  <c:v>-116584</c:v>
-                </c:pt>
-                <c:pt idx="444">
-                  <c:v>-99360</c:v>
-                </c:pt>
-                <c:pt idx="445">
-                  <c:v>-104971</c:v>
-                </c:pt>
-                <c:pt idx="446">
-                  <c:v>-100243</c:v>
-                </c:pt>
-                <c:pt idx="447">
-                  <c:v>-108464</c:v>
-                </c:pt>
-                <c:pt idx="448">
-                  <c:v>-80554</c:v>
-                </c:pt>
-                <c:pt idx="449">
-                  <c:v>-80921</c:v>
-                </c:pt>
-                <c:pt idx="450">
-                  <c:v>-81453</c:v>
-                </c:pt>
-                <c:pt idx="451">
-                  <c:v>-78722</c:v>
-                </c:pt>
-                <c:pt idx="452">
-                  <c:v>-101101</c:v>
-                </c:pt>
-                <c:pt idx="453">
-                  <c:v>-99180</c:v>
-                </c:pt>
-                <c:pt idx="454">
-                  <c:v>-97024</c:v>
-                </c:pt>
-                <c:pt idx="455">
-                  <c:v>-97153</c:v>
-                </c:pt>
-                <c:pt idx="456">
-                  <c:v>-97973</c:v>
-                </c:pt>
-                <c:pt idx="457">
-                  <c:v>-89385</c:v>
-                </c:pt>
-                <c:pt idx="458">
-                  <c:v>-102925</c:v>
-                </c:pt>
-                <c:pt idx="459">
-                  <c:v>-125577</c:v>
-                </c:pt>
-                <c:pt idx="460">
-                  <c:v>-95806</c:v>
-                </c:pt>
-                <c:pt idx="461">
-                  <c:v>-97856</c:v>
-                </c:pt>
-                <c:pt idx="462">
-                  <c:v>-98084</c:v>
-                </c:pt>
-                <c:pt idx="463">
-                  <c:v>-105445</c:v>
-                </c:pt>
-                <c:pt idx="464">
-                  <c:v>-115939</c:v>
-                </c:pt>
-                <c:pt idx="465">
-                  <c:v>-112692</c:v>
-                </c:pt>
-                <c:pt idx="466">
-                  <c:v>-112274</c:v>
-                </c:pt>
-                <c:pt idx="467">
-                  <c:v>-121667</c:v>
-                </c:pt>
-                <c:pt idx="468">
-                  <c:v>-120051</c:v>
-                </c:pt>
-                <c:pt idx="469">
-                  <c:v>-100941</c:v>
-                </c:pt>
-                <c:pt idx="470">
-                  <c:v>-105794</c:v>
-                </c:pt>
-                <c:pt idx="471">
-                  <c:v>-75163</c:v>
-                </c:pt>
-                <c:pt idx="472">
-                  <c:v>-114801</c:v>
-                </c:pt>
-                <c:pt idx="473">
-                  <c:v>-112892</c:v>
-                </c:pt>
-                <c:pt idx="474">
-                  <c:v>-113093</c:v>
-                </c:pt>
-                <c:pt idx="475">
-                  <c:v>-100932</c:v>
-                </c:pt>
-                <c:pt idx="476">
-                  <c:v>-95790</c:v>
-                </c:pt>
-                <c:pt idx="477">
-                  <c:v>-95962</c:v>
-                </c:pt>
-                <c:pt idx="478">
-                  <c:v>-95565</c:v>
-                </c:pt>
-                <c:pt idx="479">
-                  <c:v>-97524</c:v>
-                </c:pt>
-                <c:pt idx="480">
-                  <c:v>-96995</c:v>
-                </c:pt>
-                <c:pt idx="481">
-                  <c:v>-98635</c:v>
-                </c:pt>
-                <c:pt idx="482">
-                  <c:v>-134438</c:v>
-                </c:pt>
-                <c:pt idx="483">
-                  <c:v>-116925</c:v>
-                </c:pt>
-                <c:pt idx="484">
-                  <c:v>-126739</c:v>
-                </c:pt>
-                <c:pt idx="485">
-                  <c:v>-116323</c:v>
-                </c:pt>
-                <c:pt idx="486">
-                  <c:v>-117194</c:v>
-                </c:pt>
-                <c:pt idx="487">
-                  <c:v>-117619</c:v>
-                </c:pt>
-                <c:pt idx="488">
-                  <c:v>-116183</c:v>
-                </c:pt>
-                <c:pt idx="489">
-                  <c:v>-120950</c:v>
-                </c:pt>
-                <c:pt idx="490">
-                  <c:v>-116272</c:v>
-                </c:pt>
-                <c:pt idx="491">
-                  <c:v>-116430</c:v>
-                </c:pt>
-                <c:pt idx="492">
-                  <c:v>-117419</c:v>
-                </c:pt>
-                <c:pt idx="493">
-                  <c:v>-116441</c:v>
-                </c:pt>
-                <c:pt idx="494">
-                  <c:v>-111850</c:v>
-                </c:pt>
-                <c:pt idx="495">
-                  <c:v>-107435</c:v>
-                </c:pt>
-                <c:pt idx="496">
-                  <c:v>-102871</c:v>
-                </c:pt>
-                <c:pt idx="497">
-                  <c:v>-93446</c:v>
-                </c:pt>
-                <c:pt idx="498">
-                  <c:v>-111131</c:v>
-                </c:pt>
-                <c:pt idx="499">
-                  <c:v>-93841</c:v>
-                </c:pt>
-                <c:pt idx="500">
-                  <c:v>-87306</c:v>
-                </c:pt>
-                <c:pt idx="501">
-                  <c:v>-88793</c:v>
-                </c:pt>
-                <c:pt idx="502">
-                  <c:v>-96759</c:v>
-                </c:pt>
-                <c:pt idx="503">
-                  <c:v>-77104</c:v>
-                </c:pt>
-                <c:pt idx="504">
-                  <c:v>-68766</c:v>
-                </c:pt>
-                <c:pt idx="505">
-                  <c:v>-72651</c:v>
-                </c:pt>
-                <c:pt idx="506">
-                  <c:v>-78188</c:v>
-                </c:pt>
-                <c:pt idx="507">
-                  <c:v>-85427</c:v>
-                </c:pt>
-                <c:pt idx="508">
-                  <c:v>-83091</c:v>
-                </c:pt>
-                <c:pt idx="509">
-                  <c:v>-91139</c:v>
-                </c:pt>
-                <c:pt idx="510">
-                  <c:v>-83878</c:v>
-                </c:pt>
-                <c:pt idx="511">
-                  <c:v>-83442</c:v>
-                </c:pt>
-                <c:pt idx="512">
-                  <c:v>-86874</c:v>
-                </c:pt>
-                <c:pt idx="513">
-                  <c:v>-87924</c:v>
-                </c:pt>
-                <c:pt idx="514">
-                  <c:v>-85572</c:v>
-                </c:pt>
-                <c:pt idx="515">
-                  <c:v>-82993</c:v>
-                </c:pt>
-                <c:pt idx="516">
-                  <c:v>-88938</c:v>
-                </c:pt>
-                <c:pt idx="517">
-                  <c:v>-84935</c:v>
-                </c:pt>
-                <c:pt idx="518">
-                  <c:v>-84454</c:v>
-                </c:pt>
-                <c:pt idx="519">
-                  <c:v>-83461</c:v>
-                </c:pt>
-                <c:pt idx="520">
-                  <c:v>-84357</c:v>
-                </c:pt>
-                <c:pt idx="521">
-                  <c:v>-86428</c:v>
-                </c:pt>
-                <c:pt idx="522">
-                  <c:v>-87564</c:v>
-                </c:pt>
-                <c:pt idx="523">
-                  <c:v>-105732</c:v>
-                </c:pt>
-                <c:pt idx="524">
-                  <c:v>-96304</c:v>
-                </c:pt>
-                <c:pt idx="525">
-                  <c:v>-103271</c:v>
-                </c:pt>
-                <c:pt idx="526">
-                  <c:v>-79024</c:v>
-                </c:pt>
-                <c:pt idx="527">
-                  <c:v>-70597</c:v>
-                </c:pt>
-                <c:pt idx="528">
-                  <c:v>-72688</c:v>
-                </c:pt>
-                <c:pt idx="529">
-                  <c:v>-67566</c:v>
-                </c:pt>
-                <c:pt idx="530">
-                  <c:v>-74646</c:v>
-                </c:pt>
-                <c:pt idx="531">
-                  <c:v>-99680</c:v>
-                </c:pt>
-                <c:pt idx="532">
-                  <c:v>-97571</c:v>
-                </c:pt>
-                <c:pt idx="533">
-                  <c:v>-67368</c:v>
-                </c:pt>
-                <c:pt idx="534">
-                  <c:v>-66892</c:v>
-                </c:pt>
-                <c:pt idx="535">
-                  <c:v>-65735</c:v>
-                </c:pt>
-                <c:pt idx="536">
-                  <c:v>-98824</c:v>
-                </c:pt>
-                <c:pt idx="537">
-                  <c:v>-79765</c:v>
-                </c:pt>
-                <c:pt idx="538">
-                  <c:v>-87654</c:v>
-                </c:pt>
-                <c:pt idx="539">
-                  <c:v>-87400</c:v>
-                </c:pt>
-                <c:pt idx="540">
-                  <c:v>-87377</c:v>
-                </c:pt>
-                <c:pt idx="541">
-                  <c:v>-94707</c:v>
-                </c:pt>
-                <c:pt idx="542">
-                  <c:v>-88087</c:v>
-                </c:pt>
-                <c:pt idx="543">
-                  <c:v>-87101</c:v>
-                </c:pt>
-                <c:pt idx="544">
-                  <c:v>-103816</c:v>
-                </c:pt>
-                <c:pt idx="545">
-                  <c:v>-101018</c:v>
-                </c:pt>
-                <c:pt idx="546">
-                  <c:v>-98798</c:v>
-                </c:pt>
-                <c:pt idx="547">
-                  <c:v>-108838</c:v>
-                </c:pt>
-                <c:pt idx="548">
-                  <c:v>-108490</c:v>
-                </c:pt>
-                <c:pt idx="549">
-                  <c:v>-103131</c:v>
-                </c:pt>
-                <c:pt idx="550">
-                  <c:v>-99142</c:v>
-                </c:pt>
-                <c:pt idx="551">
-                  <c:v>-100070</c:v>
-                </c:pt>
-                <c:pt idx="552">
-                  <c:v>-103548</c:v>
-                </c:pt>
-                <c:pt idx="553">
-                  <c:v>-100391</c:v>
-                </c:pt>
-                <c:pt idx="554">
-                  <c:v>-104899</c:v>
-                </c:pt>
-                <c:pt idx="555">
-                  <c:v>-98279</c:v>
-                </c:pt>
-                <c:pt idx="556">
-                  <c:v>-108902</c:v>
-                </c:pt>
-                <c:pt idx="557">
-                  <c:v>-98627</c:v>
-                </c:pt>
-                <c:pt idx="558">
-                  <c:v>-101910</c:v>
-                </c:pt>
-                <c:pt idx="559">
-                  <c:v>-83449</c:v>
-                </c:pt>
-                <c:pt idx="560">
-                  <c:v>-81072</c:v>
-                </c:pt>
-                <c:pt idx="561">
-                  <c:v>-75139</c:v>
-                </c:pt>
-                <c:pt idx="562">
-                  <c:v>-80886</c:v>
-                </c:pt>
-                <c:pt idx="563">
-                  <c:v>-88282</c:v>
-                </c:pt>
-                <c:pt idx="564">
-                  <c:v>-86737</c:v>
-                </c:pt>
-                <c:pt idx="565">
-                  <c:v>-87329</c:v>
-                </c:pt>
-                <c:pt idx="566">
-                  <c:v>-99810</c:v>
-                </c:pt>
-                <c:pt idx="567">
-                  <c:v>-86664</c:v>
-                </c:pt>
-                <c:pt idx="568">
-                  <c:v>-87944</c:v>
-                </c:pt>
-                <c:pt idx="569">
-                  <c:v>-102938</c:v>
-                </c:pt>
-                <c:pt idx="570">
-                  <c:v>-98837</c:v>
-                </c:pt>
-                <c:pt idx="571">
-                  <c:v>-97949</c:v>
-                </c:pt>
-                <c:pt idx="572">
-                  <c:v>-97688</c:v>
-                </c:pt>
-                <c:pt idx="573">
-                  <c:v>-94763</c:v>
-                </c:pt>
-                <c:pt idx="574">
-                  <c:v>-123301</c:v>
-                </c:pt>
-                <c:pt idx="575">
-                  <c:v>-104132</c:v>
-                </c:pt>
-                <c:pt idx="576">
-                  <c:v>-87408</c:v>
-                </c:pt>
-                <c:pt idx="577">
-                  <c:v>-90515</c:v>
-                </c:pt>
-                <c:pt idx="578">
-                  <c:v>-86668</c:v>
-                </c:pt>
-                <c:pt idx="579">
-                  <c:v>-87590</c:v>
-                </c:pt>
-                <c:pt idx="580">
-                  <c:v>-98849</c:v>
-                </c:pt>
-                <c:pt idx="581">
-                  <c:v>-96081</c:v>
-                </c:pt>
-                <c:pt idx="582">
-                  <c:v>-96740</c:v>
-                </c:pt>
-                <c:pt idx="583">
-                  <c:v>-96129</c:v>
-                </c:pt>
-                <c:pt idx="584">
-                  <c:v>-94776</c:v>
-                </c:pt>
-                <c:pt idx="585">
-                  <c:v>-93737</c:v>
-                </c:pt>
-                <c:pt idx="586">
-                  <c:v>-97521</c:v>
-                </c:pt>
-                <c:pt idx="587">
-                  <c:v>-121744</c:v>
-                </c:pt>
-                <c:pt idx="588">
-                  <c:v>-123777</c:v>
-                </c:pt>
-                <c:pt idx="589">
-                  <c:v>-124543</c:v>
-                </c:pt>
-                <c:pt idx="590">
-                  <c:v>-124907</c:v>
-                </c:pt>
-                <c:pt idx="591">
-                  <c:v>-125011</c:v>
-                </c:pt>
-                <c:pt idx="592">
-                  <c:v>-94705</c:v>
-                </c:pt>
-                <c:pt idx="593">
-                  <c:v>-91579</c:v>
-                </c:pt>
-                <c:pt idx="594">
-                  <c:v>-124114</c:v>
-                </c:pt>
-                <c:pt idx="595">
-                  <c:v>-124773</c:v>
-                </c:pt>
-                <c:pt idx="596">
-                  <c:v>-124331</c:v>
-                </c:pt>
-                <c:pt idx="597">
-                  <c:v>-124114</c:v>
-                </c:pt>
-                <c:pt idx="598">
-                  <c:v>-124737</c:v>
-                </c:pt>
-                <c:pt idx="599">
-                  <c:v>-96044</c:v>
-                </c:pt>
-                <c:pt idx="600">
-                  <c:v>-69522</c:v>
-                </c:pt>
-                <c:pt idx="601">
-                  <c:v>-63783</c:v>
-                </c:pt>
-                <c:pt idx="602">
-                  <c:v>-68713</c:v>
-                </c:pt>
-                <c:pt idx="603">
-                  <c:v>-90297</c:v>
-                </c:pt>
-                <c:pt idx="604">
-                  <c:v>-98457</c:v>
-                </c:pt>
-                <c:pt idx="605">
-                  <c:v>-75177</c:v>
-                </c:pt>
-                <c:pt idx="606">
-                  <c:v>-73151</c:v>
-                </c:pt>
-                <c:pt idx="607">
-                  <c:v>-74703</c:v>
-                </c:pt>
-                <c:pt idx="608">
-                  <c:v>-71688</c:v>
-                </c:pt>
-                <c:pt idx="609">
-                  <c:v>-66669</c:v>
-                </c:pt>
-                <c:pt idx="610">
-                  <c:v>-57485</c:v>
-                </c:pt>
-                <c:pt idx="611">
-                  <c:v>-80021</c:v>
-                </c:pt>
-                <c:pt idx="612">
-                  <c:v>-70018</c:v>
-                </c:pt>
-                <c:pt idx="613">
-                  <c:v>-75801</c:v>
-                </c:pt>
-                <c:pt idx="614">
-                  <c:v>-60439</c:v>
-                </c:pt>
-                <c:pt idx="615">
-                  <c:v>-71358</c:v>
-                </c:pt>
-                <c:pt idx="616">
-                  <c:v>-67444</c:v>
-                </c:pt>
-                <c:pt idx="617">
-                  <c:v>-90721</c:v>
-                </c:pt>
-                <c:pt idx="618">
-                  <c:v>-78071</c:v>
-                </c:pt>
-                <c:pt idx="619">
-                  <c:v>-77794</c:v>
-                </c:pt>
-                <c:pt idx="620">
-                  <c:v>-70390</c:v>
-                </c:pt>
-                <c:pt idx="621">
-                  <c:v>-89465</c:v>
-                </c:pt>
-                <c:pt idx="622">
-                  <c:v>-66524</c:v>
-                </c:pt>
-                <c:pt idx="623">
-                  <c:v>-76687</c:v>
-                </c:pt>
-                <c:pt idx="624">
-                  <c:v>-74489</c:v>
-                </c:pt>
-                <c:pt idx="625">
-                  <c:v>-75748</c:v>
-                </c:pt>
-                <c:pt idx="626">
-                  <c:v>-68601</c:v>
-                </c:pt>
-                <c:pt idx="627">
-                  <c:v>-86313</c:v>
-                </c:pt>
-                <c:pt idx="628">
-                  <c:v>-58970</c:v>
-                </c:pt>
-                <c:pt idx="629">
-                  <c:v>-68438</c:v>
-                </c:pt>
-                <c:pt idx="630">
-                  <c:v>-63418</c:v>
-                </c:pt>
-                <c:pt idx="631">
-                  <c:v>-68879</c:v>
-                </c:pt>
-                <c:pt idx="632">
-                  <c:v>-69901</c:v>
-                </c:pt>
-                <c:pt idx="633">
-                  <c:v>-66577</c:v>
-                </c:pt>
-                <c:pt idx="634">
-                  <c:v>-74805</c:v>
-                </c:pt>
-                <c:pt idx="635">
-                  <c:v>-69048</c:v>
-                </c:pt>
-                <c:pt idx="636">
-                  <c:v>-70408</c:v>
-                </c:pt>
-                <c:pt idx="637">
-                  <c:v>-66660</c:v>
-                </c:pt>
-                <c:pt idx="638">
-                  <c:v>-66954</c:v>
-                </c:pt>
-                <c:pt idx="639">
-                  <c:v>-71544</c:v>
-                </c:pt>
-                <c:pt idx="640">
-                  <c:v>-69656</c:v>
-                </c:pt>
-                <c:pt idx="641">
-                  <c:v>-86377</c:v>
-                </c:pt>
-                <c:pt idx="642">
-                  <c:v>-67895</c:v>
-                </c:pt>
-                <c:pt idx="643">
-                  <c:v>-70088</c:v>
-                </c:pt>
-                <c:pt idx="644">
-                  <c:v>-85626</c:v>
-                </c:pt>
-                <c:pt idx="645">
-                  <c:v>-68549</c:v>
-                </c:pt>
-                <c:pt idx="646">
-                  <c:v>-65331</c:v>
-                </c:pt>
-                <c:pt idx="647">
-                  <c:v>-68950</c:v>
-                </c:pt>
-                <c:pt idx="648">
-                  <c:v>-93972</c:v>
-                </c:pt>
-                <c:pt idx="649">
-                  <c:v>-101799</c:v>
-                </c:pt>
-                <c:pt idx="650">
-                  <c:v>-76181</c:v>
-                </c:pt>
-                <c:pt idx="651">
-                  <c:v>-71230</c:v>
-                </c:pt>
-                <c:pt idx="652">
-                  <c:v>-99533</c:v>
-                </c:pt>
-                <c:pt idx="653">
-                  <c:v>-94693</c:v>
-                </c:pt>
-                <c:pt idx="654">
-                  <c:v>-94862</c:v>
-                </c:pt>
-                <c:pt idx="655">
-                  <c:v>-96157</c:v>
-                </c:pt>
-                <c:pt idx="656">
-                  <c:v>-127739</c:v>
-                </c:pt>
-                <c:pt idx="657">
-                  <c:v>-128233</c:v>
-                </c:pt>
-                <c:pt idx="658">
-                  <c:v>-128654</c:v>
-                </c:pt>
-                <c:pt idx="659">
-                  <c:v>-129657</c:v>
-                </c:pt>
-                <c:pt idx="660">
-                  <c:v>-101343</c:v>
-                </c:pt>
-                <c:pt idx="661">
-                  <c:v>-66252</c:v>
-                </c:pt>
-                <c:pt idx="662">
-                  <c:v>-97484</c:v>
-                </c:pt>
-                <c:pt idx="663">
-                  <c:v>-92541</c:v>
-                </c:pt>
-                <c:pt idx="664">
-                  <c:v>-93914</c:v>
-                </c:pt>
-                <c:pt idx="665">
-                  <c:v>-94996</c:v>
-                </c:pt>
-                <c:pt idx="666">
-                  <c:v>-93494</c:v>
-                </c:pt>
-                <c:pt idx="667">
-                  <c:v>-92853</c:v>
-                </c:pt>
-                <c:pt idx="668">
-                  <c:v>-93197</c:v>
-                </c:pt>
-                <c:pt idx="669">
-                  <c:v>-88041</c:v>
-                </c:pt>
-                <c:pt idx="670">
-                  <c:v>-83436</c:v>
-                </c:pt>
-                <c:pt idx="671">
-                  <c:v>-83424</c:v>
-                </c:pt>
-                <c:pt idx="672">
-                  <c:v>-84743</c:v>
-                </c:pt>
-                <c:pt idx="673">
-                  <c:v>-85747</c:v>
-                </c:pt>
-                <c:pt idx="674">
-                  <c:v>-81903</c:v>
-                </c:pt>
-                <c:pt idx="675">
-                  <c:v>-81483</c:v>
-                </c:pt>
-                <c:pt idx="676">
-                  <c:v>-81393</c:v>
-                </c:pt>
-                <c:pt idx="677">
-                  <c:v>-81963</c:v>
-                </c:pt>
-                <c:pt idx="678">
-                  <c:v>-82530</c:v>
-                </c:pt>
-                <c:pt idx="679">
-                  <c:v>-90128</c:v>
-                </c:pt>
-                <c:pt idx="680">
-                  <c:v>-81414</c:v>
-                </c:pt>
-                <c:pt idx="681">
-                  <c:v>-83178</c:v>
-                </c:pt>
-                <c:pt idx="682">
-                  <c:v>-81450</c:v>
-                </c:pt>
-                <c:pt idx="683">
-                  <c:v>-110927</c:v>
-                </c:pt>
-                <c:pt idx="684">
-                  <c:v>-81144</c:v>
-                </c:pt>
-                <c:pt idx="685">
-                  <c:v>-135584</c:v>
-                </c:pt>
-                <c:pt idx="686">
-                  <c:v>-86652</c:v>
-                </c:pt>
-                <c:pt idx="687">
-                  <c:v>-83130</c:v>
-                </c:pt>
-                <c:pt idx="688">
-                  <c:v>-84092</c:v>
-                </c:pt>
-                <c:pt idx="689">
-                  <c:v>-83614</c:v>
-                </c:pt>
-                <c:pt idx="690">
-                  <c:v>-101001</c:v>
-                </c:pt>
-                <c:pt idx="691">
-                  <c:v>-122013</c:v>
-                </c:pt>
-                <c:pt idx="692">
-                  <c:v>-101024</c:v>
-                </c:pt>
-                <c:pt idx="693">
-                  <c:v>-101524</c:v>
-                </c:pt>
-                <c:pt idx="694">
-                  <c:v>-101512</c:v>
-                </c:pt>
-                <c:pt idx="695">
-                  <c:v>-100814</c:v>
-                </c:pt>
-                <c:pt idx="696">
-                  <c:v>-104850</c:v>
-                </c:pt>
-                <c:pt idx="697">
-                  <c:v>-89013</c:v>
-                </c:pt>
-                <c:pt idx="698">
-                  <c:v>-83156</c:v>
-                </c:pt>
-                <c:pt idx="699">
-                  <c:v>-85427</c:v>
-                </c:pt>
-                <c:pt idx="700">
-                  <c:v>-84429</c:v>
-                </c:pt>
-                <c:pt idx="701">
-                  <c:v>-83094</c:v>
-                </c:pt>
-                <c:pt idx="702">
-                  <c:v>-84759</c:v>
-                </c:pt>
-                <c:pt idx="703">
-                  <c:v>-84820</c:v>
-                </c:pt>
-                <c:pt idx="704">
-                  <c:v>-83011</c:v>
-                </c:pt>
-                <c:pt idx="705">
-                  <c:v>-83004</c:v>
-                </c:pt>
-                <c:pt idx="706">
-                  <c:v>-82941</c:v>
-                </c:pt>
-                <c:pt idx="707">
-                  <c:v>-83364</c:v>
-                </c:pt>
-                <c:pt idx="708">
-                  <c:v>-97802</c:v>
-                </c:pt>
-                <c:pt idx="709">
-                  <c:v>-133968</c:v>
-                </c:pt>
-                <c:pt idx="710">
-                  <c:v>-132647</c:v>
-                </c:pt>
-                <c:pt idx="711">
-                  <c:v>-127233</c:v>
-                </c:pt>
-                <c:pt idx="712">
-                  <c:v>-90773</c:v>
-                </c:pt>
-                <c:pt idx="713">
-                  <c:v>-69750</c:v>
-                </c:pt>
-                <c:pt idx="714">
-                  <c:v>-90093</c:v>
-                </c:pt>
-                <c:pt idx="715">
-                  <c:v>-71683</c:v>
-                </c:pt>
-                <c:pt idx="716">
-                  <c:v>-98098</c:v>
-                </c:pt>
-                <c:pt idx="717">
-                  <c:v>-92052</c:v>
-                </c:pt>
-                <c:pt idx="718">
-                  <c:v>-106063</c:v>
-                </c:pt>
-                <c:pt idx="719">
-                  <c:v>-90203</c:v>
-                </c:pt>
-                <c:pt idx="720">
-                  <c:v>-70623</c:v>
-                </c:pt>
-                <c:pt idx="721">
-                  <c:v>-59033</c:v>
-                </c:pt>
-                <c:pt idx="722">
-                  <c:v>-88918</c:v>
-                </c:pt>
-                <c:pt idx="723">
-                  <c:v>-86528</c:v>
-                </c:pt>
-                <c:pt idx="724">
-                  <c:v>-63685</c:v>
-                </c:pt>
-                <c:pt idx="725">
-                  <c:v>-50571</c:v>
-                </c:pt>
-                <c:pt idx="726">
-                  <c:v>-46813</c:v>
-                </c:pt>
-                <c:pt idx="727">
-                  <c:v>-47874</c:v>
-                </c:pt>
-                <c:pt idx="728">
-                  <c:v>-57078</c:v>
-                </c:pt>
-                <c:pt idx="729">
-                  <c:v>-50807</c:v>
-                </c:pt>
-                <c:pt idx="730">
-                  <c:v>-54271</c:v>
-                </c:pt>
-                <c:pt idx="731">
-                  <c:v>-47201</c:v>
-                </c:pt>
-                <c:pt idx="732">
-                  <c:v>-58489</c:v>
-                </c:pt>
-                <c:pt idx="733">
-                  <c:v>-66087</c:v>
-                </c:pt>
-                <c:pt idx="734">
-                  <c:v>-74421</c:v>
-                </c:pt>
-                <c:pt idx="735">
-                  <c:v>-78885</c:v>
-                </c:pt>
-                <c:pt idx="736">
-                  <c:v>-89409</c:v>
-                </c:pt>
-                <c:pt idx="737">
-                  <c:v>-134824</c:v>
-                </c:pt>
-                <c:pt idx="738">
-                  <c:v>-91416</c:v>
-                </c:pt>
-                <c:pt idx="739">
-                  <c:v>-131192</c:v>
-                </c:pt>
-                <c:pt idx="740">
-                  <c:v>-217876</c:v>
-                </c:pt>
-                <c:pt idx="741">
-                  <c:v>-89188</c:v>
-                </c:pt>
-                <c:pt idx="742">
-                  <c:v>-100551</c:v>
-                </c:pt>
-                <c:pt idx="743">
-                  <c:v>-119418</c:v>
-                </c:pt>
-                <c:pt idx="744">
-                  <c:v>-117141</c:v>
-                </c:pt>
-                <c:pt idx="745">
-                  <c:v>-145304</c:v>
-                </c:pt>
-                <c:pt idx="746">
-                  <c:v>-92944</c:v>
-                </c:pt>
-                <c:pt idx="747">
-                  <c:v>-99535</c:v>
-                </c:pt>
-                <c:pt idx="748">
-                  <c:v>-60497</c:v>
-                </c:pt>
-                <c:pt idx="749">
-                  <c:v>-86376</c:v>
-                </c:pt>
-                <c:pt idx="750">
-                  <c:v>-232947</c:v>
-                </c:pt>
-                <c:pt idx="751">
-                  <c:v>-63905</c:v>
-                </c:pt>
-                <c:pt idx="752">
-                  <c:v>-62775</c:v>
-                </c:pt>
-                <c:pt idx="753">
-                  <c:v>-103087</c:v>
-                </c:pt>
-                <c:pt idx="754">
-                  <c:v>-50594</c:v>
-                </c:pt>
-                <c:pt idx="755">
-                  <c:v>-80885</c:v>
-                </c:pt>
-                <c:pt idx="756">
-                  <c:v>-136819</c:v>
-                </c:pt>
-                <c:pt idx="757">
-                  <c:v>-53144</c:v>
-                </c:pt>
-                <c:pt idx="758">
-                  <c:v>-59956</c:v>
-                </c:pt>
-                <c:pt idx="759">
-                  <c:v>-78806</c:v>
-                </c:pt>
-                <c:pt idx="760">
-                  <c:v>-84619</c:v>
-                </c:pt>
-                <c:pt idx="761">
-                  <c:v>-66091</c:v>
-                </c:pt>
-                <c:pt idx="762">
-                  <c:v>-52848</c:v>
-                </c:pt>
-                <c:pt idx="763">
-                  <c:v>-60813</c:v>
-                </c:pt>
-                <c:pt idx="764">
-                  <c:v>-42805</c:v>
-                </c:pt>
-                <c:pt idx="765">
-                  <c:v>-50118</c:v>
-                </c:pt>
-                <c:pt idx="766">
-                  <c:v>-47211</c:v>
+                  <c:v>760.67</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4768,7 +3415,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8876-4415-90F6-18223C997A17}"/>
+              <c16:uniqueId val="{00000000-2470-4D2F-A76B-42C09047C257}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4781,11 +3428,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="364032656"/>
-        <c:axId val="364033072"/>
+        <c:axId val="210111168"/>
+        <c:axId val="210113664"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="364032656"/>
+        <c:axId val="210111168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4827,7 +3474,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="364033072"/>
+        <c:crossAx val="210113664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4835,7 +3482,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="364033072"/>
+        <c:axId val="210113664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4886,7 +3533,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="364032656"/>
+        <c:crossAx val="210111168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5502,23 +4149,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1615440</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>312420</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>541020</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="图表 2">
+        <xdr:cNvPr id="4" name="图表 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1F9AE6F-6C41-478C-87C1-5F8658F887D8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73624BCD-7A88-4086-B3B3-0486B6918607}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5802,1277 +4449,2226 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B767"/>
+  <dimension ref="A1:E767"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>764</v>
       </c>
       <c r="B1">
         <v>-102668</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>767</v>
+      </c>
+      <c r="E1">
+        <v>888.37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>765</v>
       </c>
       <c r="B2">
         <v>-47778</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>768</v>
+      </c>
+      <c r="E2">
+        <v>665.83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>766</v>
       </c>
       <c r="B3">
         <v>-48999</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E3">
+        <v>528.83000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4">
         <v>-75036</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>770</v>
+      </c>
+      <c r="E4">
+        <v>528.83000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="B5">
         <v>-33940</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>771</v>
+      </c>
+      <c r="E5">
+        <v>528.83000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="B6">
         <v>-49695</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>772</v>
+      </c>
+      <c r="E6">
+        <v>528.83000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7">
         <v>-55880</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>773</v>
+      </c>
+      <c r="E7">
+        <v>528.83000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="B8">
         <v>-146151</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>774</v>
+      </c>
+      <c r="E8">
+        <v>529.83000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
       <c r="B9">
         <v>-169400</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>775</v>
+      </c>
+      <c r="E9">
+        <v>512.58000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
       <c r="B10">
         <v>-111323</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>776</v>
+      </c>
+      <c r="E10">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
       <c r="B11">
         <v>-105113</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>777</v>
+      </c>
+      <c r="E11">
+        <v>532.83000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
       <c r="B12">
         <v>-52333</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>778</v>
+      </c>
+      <c r="E12">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
       <c r="B13">
         <v>-114240</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>779</v>
+      </c>
+      <c r="E13">
+        <v>513.58000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
       <c r="B14">
         <v>-100915</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>780</v>
+      </c>
+      <c r="E14">
+        <v>555.91999999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
       <c r="B15">
         <v>-98380</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>781</v>
+      </c>
+      <c r="E15">
+        <v>527.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
       <c r="B16">
         <v>-67350</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>782</v>
+      </c>
+      <c r="E16">
+        <v>478.92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
       <c r="B17">
         <v>-66530</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>783</v>
+      </c>
+      <c r="E17">
+        <v>520.66999999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>14</v>
       </c>
       <c r="B18">
         <v>-119145</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>784</v>
+      </c>
+      <c r="E18">
+        <v>526.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
       <c r="B19">
         <v>-369490</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>785</v>
+      </c>
+      <c r="E19">
+        <v>478.92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
       <c r="B20">
         <v>-375488</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>786</v>
+      </c>
+      <c r="E20">
+        <v>492.58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
       <c r="B21">
         <v>-152336</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>787</v>
+      </c>
+      <c r="E21">
+        <v>508.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>18</v>
       </c>
       <c r="B22">
         <v>-152216</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>788</v>
+      </c>
+      <c r="E22">
+        <v>498.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
       <c r="B23">
         <v>-152216</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>789</v>
+      </c>
+      <c r="E23">
+        <v>501.58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
       <c r="B24">
         <v>-152216</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>790</v>
+      </c>
+      <c r="E24">
+        <v>500.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
       <c r="B25">
         <v>-149366</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>791</v>
+      </c>
+      <c r="E25">
+        <v>535.58000000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>22</v>
       </c>
       <c r="B26">
         <v>-62022</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>792</v>
+      </c>
+      <c r="E26">
+        <v>527.58000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>23</v>
       </c>
       <c r="B27">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>793</v>
+      </c>
+      <c r="E27">
+        <v>527.58000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
       <c r="B28">
         <v>-63043</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>794</v>
+      </c>
+      <c r="E28">
+        <v>531.91999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>25</v>
       </c>
       <c r="B29">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>795</v>
+      </c>
+      <c r="E29">
+        <v>530.58000000000004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>26</v>
       </c>
       <c r="B30">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>796</v>
+      </c>
+      <c r="E30">
+        <v>528.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
       <c r="B31">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>797</v>
+      </c>
+      <c r="E31">
+        <v>527.58000000000004</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>28</v>
       </c>
       <c r="B32">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>798</v>
+      </c>
+      <c r="E32">
+        <v>530.58000000000004</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>29</v>
       </c>
       <c r="B33">
         <v>-62623</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>799</v>
+      </c>
+      <c r="E33">
+        <v>531.58000000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>30</v>
       </c>
       <c r="B34">
         <v>-62188</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>800</v>
+      </c>
+      <c r="E34">
+        <v>527.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>31</v>
       </c>
       <c r="B35">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>801</v>
+      </c>
+      <c r="E35">
+        <v>527.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>32</v>
       </c>
       <c r="B36">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>802</v>
+      </c>
+      <c r="E36">
+        <v>527.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>33</v>
       </c>
       <c r="B37">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>803</v>
+      </c>
+      <c r="E37">
+        <v>556.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>34</v>
       </c>
       <c r="B38">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>804</v>
+      </c>
+      <c r="E38">
+        <v>540.16999999999996</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>35</v>
       </c>
       <c r="B39">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>805</v>
+      </c>
+      <c r="E39">
+        <v>883.72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>36</v>
       </c>
       <c r="B40">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>806</v>
+      </c>
+      <c r="E40">
+        <v>826.33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>37</v>
       </c>
       <c r="B41">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>807</v>
+      </c>
+      <c r="E41">
+        <v>811.33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>38</v>
       </c>
       <c r="B42">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>808</v>
+      </c>
+      <c r="E42">
+        <v>823.67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>39</v>
       </c>
       <c r="B43">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>809</v>
+      </c>
+      <c r="E43">
+        <v>811.33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>40</v>
       </c>
       <c r="B44">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>810</v>
+      </c>
+      <c r="E44">
+        <v>813.67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>41</v>
       </c>
       <c r="B45">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>811</v>
+      </c>
+      <c r="E45">
+        <v>811.33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>42</v>
       </c>
       <c r="B46">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>812</v>
+      </c>
+      <c r="E46">
+        <v>820.67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>43</v>
       </c>
       <c r="B47">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>813</v>
+      </c>
+      <c r="E47">
+        <v>813.67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>44</v>
       </c>
       <c r="B48">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>814</v>
+      </c>
+      <c r="E48">
+        <v>811.33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>45</v>
       </c>
       <c r="B49">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>815</v>
+      </c>
+      <c r="E49">
+        <v>813.67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>46</v>
       </c>
       <c r="B50">
         <v>-60663</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>816</v>
+      </c>
+      <c r="E50">
+        <v>811.33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>47</v>
       </c>
       <c r="B51">
         <v>-61779</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>817</v>
+      </c>
+      <c r="E51">
+        <v>811.33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>48</v>
       </c>
       <c r="B52">
         <v>-61935</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>818</v>
+      </c>
+      <c r="E52">
+        <v>769.17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>49</v>
       </c>
       <c r="B53">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>819</v>
+      </c>
+      <c r="E53">
+        <v>797.85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>50</v>
       </c>
       <c r="B54">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>820</v>
+      </c>
+      <c r="E54">
+        <v>555.25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>51</v>
       </c>
       <c r="B55">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>821</v>
+      </c>
+      <c r="E55">
+        <v>791.92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>52</v>
       </c>
       <c r="B56">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>822</v>
+      </c>
+      <c r="E56">
+        <v>528.83000000000004</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>53</v>
       </c>
       <c r="B57">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>823</v>
+      </c>
+      <c r="E57">
+        <v>531.66999999999996</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>54</v>
       </c>
       <c r="B58">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>824</v>
+      </c>
+      <c r="E58">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>55</v>
       </c>
       <c r="B59">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>825</v>
+      </c>
+      <c r="E59">
+        <v>876.17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>56</v>
       </c>
       <c r="B60">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>826</v>
+      </c>
+      <c r="E60">
+        <v>864.83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>57</v>
       </c>
       <c r="B61">
         <v>-63422</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>827</v>
+      </c>
+      <c r="E61">
+        <v>872.17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>58</v>
       </c>
       <c r="B62">
         <v>-68603</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>828</v>
+      </c>
+      <c r="E62">
+        <v>870.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>59</v>
       </c>
       <c r="B63">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>829</v>
+      </c>
+      <c r="E63">
+        <v>870.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>60</v>
       </c>
       <c r="B64">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>830</v>
+      </c>
+      <c r="E64">
+        <v>880.67</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>61</v>
       </c>
       <c r="B65">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>831</v>
+      </c>
+      <c r="E65">
+        <v>878.67</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>62</v>
       </c>
       <c r="B66">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>832</v>
+      </c>
+      <c r="E66">
+        <v>879.67</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>63</v>
       </c>
       <c r="B67">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>833</v>
+      </c>
+      <c r="E67">
+        <v>865.67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>64</v>
       </c>
       <c r="B68">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>834</v>
+      </c>
+      <c r="E68">
+        <v>885.08</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>65</v>
       </c>
       <c r="B69">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>835</v>
+      </c>
+      <c r="E69">
+        <v>884.17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>66</v>
       </c>
       <c r="B70">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>836</v>
+      </c>
+      <c r="E70">
+        <v>904.25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>67</v>
       </c>
       <c r="B71">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>837</v>
+      </c>
+      <c r="E71">
+        <v>869.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>68</v>
       </c>
       <c r="B72">
         <v>-61853</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>838</v>
+      </c>
+      <c r="E72">
+        <v>892.63</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>69</v>
       </c>
       <c r="B73">
         <v>-62133</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>839</v>
+      </c>
+      <c r="E73">
+        <v>873.33</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>70</v>
       </c>
       <c r="B74">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>840</v>
+      </c>
+      <c r="E74">
+        <v>884.55</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>71</v>
       </c>
       <c r="B75">
         <v>-62013</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>841</v>
+      </c>
+      <c r="E75">
+        <v>846.83</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>72</v>
       </c>
       <c r="B76">
         <v>-114173</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>842</v>
+      </c>
+      <c r="E76">
+        <v>864.45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>73</v>
       </c>
       <c r="B77">
         <v>-194909</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>843</v>
+      </c>
+      <c r="E77">
+        <v>642.25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>74</v>
       </c>
       <c r="B78">
         <v>-121118</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>844</v>
+      </c>
+      <c r="E78">
+        <v>661.72</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>75</v>
       </c>
       <c r="B79">
         <v>-91716</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>845</v>
+      </c>
+      <c r="E79">
+        <v>873.25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>76</v>
       </c>
       <c r="B80">
         <v>-95531</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
+        <v>846</v>
+      </c>
+      <c r="E80">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>77</v>
       </c>
       <c r="B81">
         <v>-144210</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D81" t="s">
+        <v>847</v>
+      </c>
+      <c r="E81">
+        <v>739.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>78</v>
       </c>
       <c r="B82">
         <v>-61366</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>848</v>
+      </c>
+      <c r="E82">
+        <v>876.08</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>79</v>
       </c>
       <c r="B83">
         <v>-79363</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
+        <v>849</v>
+      </c>
+      <c r="E83">
+        <v>862.67</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>80</v>
       </c>
       <c r="B84">
         <v>-92303</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>850</v>
+      </c>
+      <c r="E84">
+        <v>874.83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>81</v>
       </c>
       <c r="B85">
         <v>-62100</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>851</v>
+      </c>
+      <c r="E85">
+        <v>864.33</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>82</v>
       </c>
       <c r="B86">
         <v>-37518</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>852</v>
+      </c>
+      <c r="E86">
+        <v>864.83</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>83</v>
       </c>
       <c r="B87">
         <v>-24898</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>853</v>
+      </c>
+      <c r="E87">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>84</v>
       </c>
       <c r="B88">
         <v>-64572</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>854</v>
+      </c>
+      <c r="E88">
+        <v>872.62</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>85</v>
       </c>
       <c r="B89">
         <v>-75174</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D89" t="s">
+        <v>855</v>
+      </c>
+      <c r="E89">
+        <v>865.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>86</v>
       </c>
       <c r="B90">
         <v>-19923</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
+        <v>856</v>
+      </c>
+      <c r="E90">
+        <v>875.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>87</v>
       </c>
       <c r="B91">
         <v>-54694</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D91" t="s">
+        <v>857</v>
+      </c>
+      <c r="E91">
+        <v>866.25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>88</v>
       </c>
       <c r="B92">
         <v>-67323</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
+        <v>858</v>
+      </c>
+      <c r="E92">
+        <v>859.67</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>89</v>
       </c>
       <c r="B93">
         <v>-75941</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
+        <v>859</v>
+      </c>
+      <c r="E93">
+        <v>859.67</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>90</v>
       </c>
       <c r="B94">
         <v>-32440</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>860</v>
+      </c>
+      <c r="E94">
+        <v>528.83000000000004</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>91</v>
       </c>
       <c r="B95">
         <v>-66007</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>861</v>
+      </c>
+      <c r="E95">
+        <v>871.33</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>92</v>
       </c>
       <c r="B96">
         <v>-79504</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>862</v>
+      </c>
+      <c r="E96">
+        <v>864.83</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>93</v>
       </c>
       <c r="B97">
         <v>-25843</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>863</v>
+      </c>
+      <c r="E97">
+        <v>664.83</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>94</v>
       </c>
       <c r="B98">
         <v>-25723</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>864</v>
+      </c>
+      <c r="E98">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>95</v>
       </c>
       <c r="B99">
         <v>-25723</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
+        <v>865</v>
+      </c>
+      <c r="E99">
+        <v>877.5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>96</v>
       </c>
       <c r="B100">
         <v>-25723</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>866</v>
+      </c>
+      <c r="E100">
+        <v>867.33</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>97</v>
       </c>
       <c r="B101">
         <v>-25723</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>867</v>
+      </c>
+      <c r="E101">
+        <v>865.22</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>98</v>
       </c>
       <c r="B102">
         <v>-25723</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
+        <v>868</v>
+      </c>
+      <c r="E102">
+        <v>868.58</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>99</v>
       </c>
       <c r="B103">
         <v>-25723</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
+        <v>869</v>
+      </c>
+      <c r="E103">
+        <v>652.66999999999996</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>100</v>
       </c>
       <c r="B104">
         <v>-25723</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
+        <v>870</v>
+      </c>
+      <c r="E104">
+        <v>892.32</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>101</v>
       </c>
       <c r="B105">
         <v>-25723</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
+        <v>871</v>
+      </c>
+      <c r="E105">
+        <v>883.33</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>102</v>
       </c>
       <c r="B106">
         <v>-25723</v>
       </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
+        <v>872</v>
+      </c>
+      <c r="E106">
+        <v>867.67</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>103</v>
       </c>
       <c r="B107">
         <v>-25723</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>873</v>
+      </c>
+      <c r="E107">
+        <v>873.33</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>104</v>
       </c>
       <c r="B108">
         <v>-27947</v>
       </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>874</v>
+      </c>
+      <c r="E108">
+        <v>876.17</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>105</v>
       </c>
       <c r="B109">
         <v>-50259</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
+        <v>875</v>
+      </c>
+      <c r="E109">
+        <v>880.58</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>106</v>
       </c>
       <c r="B110">
         <v>-42419</v>
       </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>876</v>
+      </c>
+      <c r="E110">
+        <v>868.9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>107</v>
       </c>
       <c r="B111">
         <v>-38669</v>
       </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>877</v>
+      </c>
+      <c r="E111">
+        <v>878.67</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>108</v>
       </c>
       <c r="B112">
         <v>-43949</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
+        <v>878</v>
+      </c>
+      <c r="E112">
+        <v>898.3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>109</v>
       </c>
       <c r="B113">
         <v>-53356</v>
       </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D113" t="s">
+        <v>879</v>
+      </c>
+      <c r="E113">
+        <v>658.83</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>110</v>
       </c>
       <c r="B114">
         <v>-82092</v>
       </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D114" t="s">
+        <v>880</v>
+      </c>
+      <c r="E114">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>111</v>
       </c>
       <c r="B115">
         <v>-77645</v>
       </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
+        <v>881</v>
+      </c>
+      <c r="E115">
+        <v>861.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>112</v>
       </c>
       <c r="B116">
         <v>-33029</v>
       </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D116" t="s">
+        <v>882</v>
+      </c>
+      <c r="E116">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>113</v>
       </c>
       <c r="B117">
         <v>-67099</v>
       </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D117" t="s">
+        <v>883</v>
+      </c>
+      <c r="E117">
+        <v>887.6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>114</v>
       </c>
       <c r="B118">
         <v>-71484</v>
       </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D118" t="s">
+        <v>884</v>
+      </c>
+      <c r="E118">
+        <v>882.65</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>115</v>
       </c>
       <c r="B119">
         <v>-56424</v>
       </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D119" t="s">
+        <v>885</v>
+      </c>
+      <c r="E119">
+        <v>895.03</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>116</v>
       </c>
       <c r="B120">
         <v>-56433</v>
       </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D120" t="s">
+        <v>886</v>
+      </c>
+      <c r="E120">
+        <v>878.67</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>117</v>
       </c>
       <c r="B121">
         <v>-55444</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D121" t="s">
+        <v>887</v>
+      </c>
+      <c r="E121">
+        <v>878.67</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>118</v>
       </c>
       <c r="B122">
         <v>-70568</v>
       </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D122" t="s">
+        <v>888</v>
+      </c>
+      <c r="E122">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>119</v>
       </c>
       <c r="B123">
         <v>-55907</v>
       </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D123" t="s">
+        <v>889</v>
+      </c>
+      <c r="E123">
+        <v>870.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>120</v>
       </c>
       <c r="B124">
         <v>-70062</v>
       </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D124" t="s">
+        <v>890</v>
+      </c>
+      <c r="E124">
+        <v>867.67</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>121</v>
       </c>
       <c r="B125">
         <v>-55836</v>
       </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D125" t="s">
+        <v>891</v>
+      </c>
+      <c r="E125">
+        <v>867.67</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>122</v>
       </c>
       <c r="B126">
         <v>-60189</v>
       </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D126" t="s">
+        <v>892</v>
+      </c>
+      <c r="E126">
+        <v>552.83000000000004</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>123</v>
       </c>
       <c r="B127">
         <v>-100259</v>
       </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D127" t="s">
+        <v>893</v>
+      </c>
+      <c r="E127">
+        <v>877.67</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>124</v>
       </c>
       <c r="B128">
         <v>-63723</v>
       </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D128" t="s">
+        <v>894</v>
+      </c>
+      <c r="E128">
+        <v>867.67</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>125</v>
       </c>
       <c r="B129">
         <v>-64978</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D129" t="s">
+        <v>895</v>
+      </c>
+      <c r="E129">
+        <v>873.33</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>126</v>
       </c>
       <c r="B130">
         <v>-63661</v>
       </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D130" t="s">
+        <v>896</v>
+      </c>
+      <c r="E130">
+        <v>867.67</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>127</v>
       </c>
       <c r="B131">
         <v>-69954</v>
       </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D131" t="s">
+        <v>897</v>
+      </c>
+      <c r="E131">
+        <v>867.67</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>128</v>
       </c>
       <c r="B132">
         <v>-64978</v>
       </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D132" t="s">
+        <v>898</v>
+      </c>
+      <c r="E132">
+        <v>844.5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>129</v>
       </c>
       <c r="B133">
         <v>-69824</v>
       </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D133" t="s">
+        <v>899</v>
+      </c>
+      <c r="E133">
+        <v>669.67</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>130</v>
       </c>
       <c r="B134">
         <v>-104085</v>
       </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D134" t="s">
+        <v>900</v>
+      </c>
+      <c r="E134">
+        <v>555.16999999999996</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>131</v>
       </c>
       <c r="B135">
         <v>-58706</v>
       </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D135" t="s">
+        <v>901</v>
+      </c>
+      <c r="E135">
+        <v>654.33000000000004</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>132</v>
       </c>
       <c r="B136">
         <v>-61958</v>
       </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D136" t="s">
+        <v>902</v>
+      </c>
+      <c r="E136">
+        <v>648.33000000000004</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>133</v>
       </c>
       <c r="B137">
         <v>-81998</v>
       </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D137" t="s">
+        <v>903</v>
+      </c>
+      <c r="E137">
+        <v>880.02</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>134</v>
       </c>
       <c r="B138">
         <v>-56018</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D138" t="s">
+        <v>904</v>
+      </c>
+      <c r="E138">
+        <v>706.92</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>135</v>
       </c>
       <c r="B139">
         <v>-56266</v>
       </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D139" t="s">
+        <v>905</v>
+      </c>
+      <c r="E139">
+        <v>705.08</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>136</v>
       </c>
       <c r="B140">
         <v>-56553</v>
       </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D140" t="s">
+        <v>906</v>
+      </c>
+      <c r="E140">
+        <v>880.25</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>137</v>
       </c>
       <c r="B141">
         <v>-67524</v>
       </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D141" t="s">
+        <v>907</v>
+      </c>
+      <c r="E141">
+        <v>869.17</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>138</v>
       </c>
       <c r="B142">
         <v>-56138</v>
       </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D142" t="s">
+        <v>908</v>
+      </c>
+      <c r="E142">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>139</v>
       </c>
       <c r="B143">
         <v>-91139</v>
       </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D143" t="s">
+        <v>909</v>
+      </c>
+      <c r="E143">
+        <v>737.17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>140</v>
       </c>
       <c r="B144">
         <v>-87738</v>
       </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D144" t="s">
+        <v>910</v>
+      </c>
+      <c r="E144">
+        <v>737.17</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>141</v>
       </c>
       <c r="B145">
         <v>-87718</v>
       </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D145" t="s">
+        <v>911</v>
+      </c>
+      <c r="E145">
+        <v>737.17</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>142</v>
       </c>
       <c r="B146">
         <v>-87638</v>
       </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D146" t="s">
+        <v>912</v>
+      </c>
+      <c r="E146">
+        <v>737.17</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>143</v>
       </c>
       <c r="B147">
         <v>-87638</v>
       </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D147" t="s">
+        <v>913</v>
+      </c>
+      <c r="E147">
+        <v>737.17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>144</v>
       </c>
       <c r="B148">
         <v>-84768</v>
       </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D148" t="s">
+        <v>914</v>
+      </c>
+      <c r="E148">
+        <v>737.17</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>145</v>
       </c>
       <c r="B149">
         <v>-68098</v>
       </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D149" t="s">
+        <v>915</v>
+      </c>
+      <c r="E149">
+        <v>740.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>146</v>
       </c>
       <c r="B150">
         <v>-68128</v>
       </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D150" t="s">
+        <v>916</v>
+      </c>
+      <c r="E150">
+        <v>869.92</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>147</v>
       </c>
       <c r="B151">
         <v>-88368</v>
       </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D151" t="s">
+        <v>917</v>
+      </c>
+      <c r="E151">
+        <v>866.58</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>148</v>
       </c>
       <c r="B152">
         <v>-125516</v>
       </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D152" t="s">
+        <v>918</v>
+      </c>
+      <c r="E152">
+        <v>885.9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>149</v>
       </c>
       <c r="B153">
         <v>-89523</v>
       </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D153" t="s">
+        <v>919</v>
+      </c>
+      <c r="E153">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>150</v>
       </c>
       <c r="B154">
         <v>-86431</v>
       </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D154" t="s">
+        <v>920</v>
+      </c>
+      <c r="E154">
+        <v>856.33</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>151</v>
       </c>
       <c r="B155">
         <v>-69350</v>
       </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D155" t="s">
+        <v>921</v>
+      </c>
+      <c r="E155">
+        <v>593.58000000000004</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>152</v>
       </c>
       <c r="B156">
         <v>-72928</v>
       </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D156" t="s">
+        <v>922</v>
+      </c>
+      <c r="E156">
+        <v>845.67</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>153</v>
       </c>
       <c r="B157">
         <v>-86128</v>
       </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D157" t="s">
+        <v>923</v>
+      </c>
+      <c r="E157">
+        <v>770.83</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>154</v>
       </c>
       <c r="B158">
         <v>-87266</v>
       </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D158" t="s">
+        <v>924</v>
+      </c>
+      <c r="E158">
+        <v>760.67</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>155</v>
       </c>
@@ -7080,7 +6676,7 @@
         <v>-83644</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>156</v>
       </c>
